--- a/重点品类洞察-管理者补充信息收集表-V2-已填写.xlsx
+++ b/重点品类洞察-管理者补充信息收集表-V2-已填写.xlsx
@@ -891,7 +891,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1004,6 +1004,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1819,7 +1830,7 @@
       </c>
       <c r="B14" s="26" t="inlineStr">
         <is>
-          <t>基线数据来自工作台 V2.9（v5-1.xlsx），2026 年 2-9 月累计。</t>
+          <t>基线数据来自工作台 V2.9（v5-1.xlsx），2026 年 2-9 月累计。；2026-10-24 更新：各品类 sheet 改以领星利润报表-MSKU（2026-01-01~10-24）为主口径，汇总见「01 汇总」N–X 列。</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1878,7 @@
       </c>
       <c r="B19" s="34" t="inlineStr">
         <is>
-          <t>本版黄色单元格已按以下资料预填，供管理者确认/修改：工作台 V2.9 基线；充气泵品线看板与形态总览（卖家精灵 TOP200，2026-10-17）；油泵品线月度复盘（2026-10-23）；黄油枪评论汇总（2026-10-20）；卖家精灵 ABA 月度搜索趋势（US，截至 2026-09）。责任人填写的是岗位，需替换为具体姓名；金额为估算区间。V1 与 V2.9 口径冲突处已在「判断/量化修正」列标出。</t>
+          <t>本版黄色单元格已按以下资料预填，供管理者确认/修改：领星利润报表-MSKU 与 ASIN 日报（2026-01-01~10-24，主口径）；工作台 V2.9 基线；充气泵品线看板与形态总览（卖家精灵 TOP200，2026-10-17）；油泵品线月度复盘（2026-10-23）；黄油枪评论汇总（2026-10-20）；卖家精灵 ABA 月度搜索趋势（US，截至 2026-09）。责任人填写的是岗位，需替换为具体姓名；金额为估算区间。V1 与 V2.9 口径冲突处已在「判断/量化修正」列标出。</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:X11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="7"/>
   <cols>
     <col width="10" customWidth="1" style="33" min="1" max="1"/>
@@ -1894,9 +1905,20 @@
     <col width="14" customWidth="1" style="33" min="3" max="3"/>
     <col width="12" customWidth="1" style="33" min="4" max="6"/>
     <col width="14" customWidth="1" style="33" min="7" max="12"/>
+    <col width="13" customWidth="1" style="33" min="14" max="14"/>
+    <col width="13" customWidth="1" style="33" min="15" max="15"/>
+    <col width="13" customWidth="1" style="33" min="16" max="16"/>
+    <col width="13" customWidth="1" style="33" min="17" max="17"/>
+    <col width="13" customWidth="1" style="33" min="18" max="18"/>
+    <col width="13" customWidth="1" style="33" min="19" max="19"/>
+    <col width="13" customWidth="1" style="33" min="20" max="20"/>
+    <col width="13" customWidth="1" style="33" min="21" max="21"/>
+    <col width="13" customWidth="1" style="33" min="22" max="22"/>
+    <col width="13" customWidth="1" style="33" min="23" max="23"/>
+    <col width="13" customWidth="1" style="33" min="24" max="24"/>
   </cols>
   <sheetData>
-    <row r="1" ht="32" customHeight="1" s="33">
+    <row r="1" ht="36" customHeight="1" s="33">
       <c r="A1" s="3" t="inlineStr">
         <is>
           <t>品类</t>
@@ -1955,6 +1977,62 @@
       <c r="L1" s="3" t="inlineStr">
         <is>
           <t>品类整体优先级</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>销售额(USD)
+1/1–10/24</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>占公司%</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>毛利额(USD)</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>毛利额占比%</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>毛利率%</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>广告花费(USD)</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>广告占公司%</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>广告费率%</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>ASIN 数</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>负毛利ASIN数</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>负毛利ASIN占比%</t>
         </is>
       </c>
     </row>
@@ -2008,6 +2086,39 @@
           <t>无需填写</t>
         </is>
       </c>
+      <c r="N2" s="42" t="n">
+        <v>3843776</v>
+      </c>
+      <c r="O2" s="43" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="P2" s="42" t="n">
+        <v>319672</v>
+      </c>
+      <c r="Q2" s="43" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="R2" s="43" t="n">
+        <v>8.32</v>
+      </c>
+      <c r="S2" s="42" t="n">
+        <v>664904</v>
+      </c>
+      <c r="T2" s="43" t="n">
+        <v>13.73</v>
+      </c>
+      <c r="U2" s="43" t="n">
+        <v>17.3</v>
+      </c>
+      <c r="V2" s="42" t="n">
+        <v>91</v>
+      </c>
+      <c r="W2" s="42" t="n">
+        <v>44</v>
+      </c>
+      <c r="X2" s="43" t="n">
+        <v>48.35</v>
+      </c>
     </row>
     <row r="3" ht="14.65" customHeight="1" s="33">
       <c r="A3" s="18" t="inlineStr">
@@ -2054,6 +2165,39 @@
           <t>无需填写</t>
         </is>
       </c>
+      <c r="N3" s="42" t="n">
+        <v>2397144</v>
+      </c>
+      <c r="O3" s="43" t="n">
+        <v>7.34</v>
+      </c>
+      <c r="P3" s="42" t="n">
+        <v>609510</v>
+      </c>
+      <c r="Q3" s="43" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="R3" s="43" t="n">
+        <v>25.43</v>
+      </c>
+      <c r="S3" s="42" t="n">
+        <v>258949</v>
+      </c>
+      <c r="T3" s="43" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="U3" s="43" t="n">
+        <v>10.8</v>
+      </c>
+      <c r="V3" s="42" t="n">
+        <v>28</v>
+      </c>
+      <c r="W3" s="42" t="n">
+        <v>5</v>
+      </c>
+      <c r="X3" s="43" t="n">
+        <v>17.86</v>
+      </c>
     </row>
     <row r="4" ht="14.65" customHeight="1" s="33">
       <c r="A4" s="18" t="inlineStr">
@@ -2100,6 +2244,39 @@
           <t>无需填写</t>
         </is>
       </c>
+      <c r="N4" s="42" t="n">
+        <v>3088508</v>
+      </c>
+      <c r="O4" s="43" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="P4" s="42" t="n">
+        <v>586484</v>
+      </c>
+      <c r="Q4" s="43" t="n">
+        <v>13.04</v>
+      </c>
+      <c r="R4" s="43" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="S4" s="42" t="n">
+        <v>452613</v>
+      </c>
+      <c r="T4" s="43" t="n">
+        <v>9.35</v>
+      </c>
+      <c r="U4" s="43" t="n">
+        <v>14.65</v>
+      </c>
+      <c r="V4" s="42" t="n">
+        <v>132</v>
+      </c>
+      <c r="W4" s="42" t="n">
+        <v>29</v>
+      </c>
+      <c r="X4" s="43" t="n">
+        <v>21.97</v>
+      </c>
     </row>
     <row r="5" ht="14.65" customHeight="1" s="33">
       <c r="A5" s="18" t="inlineStr">
@@ -2146,6 +2323,39 @@
           <t>无需填写</t>
         </is>
       </c>
+      <c r="N5" s="42" t="n">
+        <v>3339273</v>
+      </c>
+      <c r="O5" s="43" t="n">
+        <v>10.22</v>
+      </c>
+      <c r="P5" s="42" t="n">
+        <v>433333</v>
+      </c>
+      <c r="Q5" s="43" t="n">
+        <v>9.630000000000001</v>
+      </c>
+      <c r="R5" s="43" t="n">
+        <v>12.98</v>
+      </c>
+      <c r="S5" s="42" t="n">
+        <v>536394</v>
+      </c>
+      <c r="T5" s="43" t="n">
+        <v>11.08</v>
+      </c>
+      <c r="U5" s="43" t="n">
+        <v>16.06</v>
+      </c>
+      <c r="V5" s="42" t="n">
+        <v>67</v>
+      </c>
+      <c r="W5" s="42" t="n">
+        <v>16</v>
+      </c>
+      <c r="X5" s="43" t="n">
+        <v>23.88</v>
+      </c>
     </row>
     <row r="6" ht="14.65" customHeight="1" s="33">
       <c r="A6" s="18" t="inlineStr">
@@ -2192,6 +2402,39 @@
           <t>无需填写</t>
         </is>
       </c>
+      <c r="N6" s="42" t="n">
+        <v>1710643</v>
+      </c>
+      <c r="O6" s="43" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="P6" s="42" t="n">
+        <v>201375</v>
+      </c>
+      <c r="Q6" s="43" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="R6" s="43" t="n">
+        <v>11.77</v>
+      </c>
+      <c r="S6" s="42" t="n">
+        <v>253472</v>
+      </c>
+      <c r="T6" s="43" t="n">
+        <v>5.24</v>
+      </c>
+      <c r="U6" s="43" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="V6" s="42" t="n">
+        <v>51</v>
+      </c>
+      <c r="W6" s="42" t="n">
+        <v>10</v>
+      </c>
+      <c r="X6" s="43" t="n">
+        <v>19.61</v>
+      </c>
     </row>
     <row r="7" ht="14.65" customHeight="1" s="33">
       <c r="A7" s="18" t="inlineStr">
@@ -2238,6 +2481,39 @@
           <t>无需填写</t>
         </is>
       </c>
+      <c r="N7" s="42" t="n">
+        <v>1628745</v>
+      </c>
+      <c r="O7" s="43" t="n">
+        <v>4.98</v>
+      </c>
+      <c r="P7" s="42" t="n">
+        <v>307133</v>
+      </c>
+      <c r="Q7" s="43" t="n">
+        <v>6.83</v>
+      </c>
+      <c r="R7" s="43" t="n">
+        <v>18.86</v>
+      </c>
+      <c r="S7" s="42" t="n">
+        <v>264340</v>
+      </c>
+      <c r="T7" s="43" t="n">
+        <v>5.46</v>
+      </c>
+      <c r="U7" s="43" t="n">
+        <v>16.23</v>
+      </c>
+      <c r="V7" s="42" t="n">
+        <v>17</v>
+      </c>
+      <c r="W7" s="42" t="n">
+        <v>3</v>
+      </c>
+      <c r="X7" s="43" t="n">
+        <v>17.65</v>
+      </c>
     </row>
     <row r="8" ht="14.65" customHeight="1" s="33">
       <c r="A8" s="18" t="inlineStr">
@@ -2284,8 +2560,82 @@
           <t>无需填写</t>
         </is>
       </c>
+      <c r="N8" s="42" t="n">
+        <v>3420029</v>
+      </c>
+      <c r="O8" s="43" t="n">
+        <v>10.47</v>
+      </c>
+      <c r="P8" s="42" t="n">
+        <v>495166</v>
+      </c>
+      <c r="Q8" s="43" t="n">
+        <v>11.01</v>
+      </c>
+      <c r="R8" s="43" t="n">
+        <v>14.48</v>
+      </c>
+      <c r="S8" s="42" t="n">
+        <v>467865</v>
+      </c>
+      <c r="T8" s="43" t="n">
+        <v>9.66</v>
+      </c>
+      <c r="U8" s="43" t="n">
+        <v>13.68</v>
+      </c>
+      <c r="V8" s="42" t="n">
+        <v>103</v>
+      </c>
+      <c r="W8" s="42" t="n">
+        <v>21</v>
+      </c>
+      <c r="X8" s="43" t="n">
+        <v>20.39</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>公司合计（利润表）</t>
+        </is>
+      </c>
+      <c r="N9" s="44" t="n">
+        <v>32675390</v>
+      </c>
+      <c r="O9" s="45" t="n">
+        <v>100</v>
+      </c>
+      <c r="P9" s="44" t="n">
+        <v>4499112</v>
+      </c>
+      <c r="Q9" s="45" t="n">
+        <v>100</v>
+      </c>
+      <c r="R9" s="45" t="n">
+        <v>13.77</v>
+      </c>
+      <c r="S9" s="44" t="n">
+        <v>4841738</v>
+      </c>
+      <c r="T9" s="45" t="n">
+        <v>100</v>
+      </c>
+      <c r="U9" s="45" t="n">
+        <v>14.82</v>
+      </c>
+    </row>
+    <row r="11" ht="48" customHeight="1" s="33">
+      <c r="A11" s="46" t="inlineStr">
+        <is>
+          <t>说明：B–F 列为原工作台 V2.9 基线（2–9 月）；N–X 列为领星利润报表-MSKU（2026-01-01~10-24，全站点，USD）汇总：销售额=FBA+FBM 销售额，广告=SP+SB+SBV+SD，ASIN 按去重合并计，负毛利=合并后毛利润&lt;0；品类映射：钉枪=木工钉枪，黄油枪含黄油枪配件，灯具=全部灯具。两套口径差异较大（如冲击扳手 $438K vs $3.42M），各品类 sheet 已改用利润表口径。</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A11:X11"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2407,7 +2757,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="132" customHeight="1" s="33">
+    <row r="4" ht="146" customHeight="1" s="33">
       <c r="A4" s="4" t="n">
         <v>1</v>
       </c>
@@ -2434,37 +2784,37 @@
       </c>
       <c r="G4" s="35" t="inlineStr">
         <is>
-          <t>工作台 V2.9 基线（2–9 月累计）：逆变器销售额 $4,954,007、占公司 19.07%、毛利率 16.31%、广告费率 13.99%、105 个 ASIN；与 V1「毛利率 0.44%、62 个 ASIN、收入约 $4.28M」差距 15.9pct。</t>
+          <t>利润表（领星利润报表-MSKU，2026-01-01~10-24）：销售额 $3,843,776（占公司 11.76%），毛利 $319,672（占公司 7.11%），毛利率 8.32%，比公司 13.77% 低 5.45pct；广告费率 17.30%（公司 14.82%）。</t>
         </is>
       </c>
       <c r="H4" s="35" t="inlineStr">
         <is>
-          <t>以 V2.9 为准，品类毛利率 16.31% 高于公司均值 12.30%，「结构性亏损」需复核后再下结论。来源：工作台 V2.9（v5-1.xlsx）</t>
+          <t>毛利率修正为 8.32%：不是 V1 的 0.44%，也不是 V2.9 的 16.31%；「收入占比高、毛利占比低」的结构判断成立。按公司毛利率应有约 $529K 毛利，实际 $320K，缺口约 $209K（10 个月口径）。</t>
         </is>
       </c>
       <c r="I4" s="35" t="inlineStr">
         <is>
-          <t>两版口径不一致：ASIN 范围（62 vs 105）不同；V1 可能扣除了广告/退货/仓储费（净毛利），V2.9 为订单毛利。</t>
+          <t>200W 段占 78.1% 销售额、毛利率仅 9.3%；350W（GM −12.3%）、300W（GM −8.6%）、修正波款（GM −13.2%）拖累。</t>
         </is>
       </c>
       <c r="J4" s="35" t="inlineStr">
         <is>
-          <t>1) 数据组+财务出两版口径对照表（ASIN 清单/期间/费用项）；2) 后续按 ASIN 同时列订单毛利与净毛利。</t>
+          <t>1) 200W 主力款降广告、提价测试；2) 350W/300W/修正波款止损；3) 550W（GM 17.6%、广告 9.0%）作为利润款加投。</t>
         </is>
       </c>
       <c r="K4" s="35" t="inlineStr">
         <is>
-          <t>数据分析 / 财务BP</t>
+          <t>品类负责人</t>
         </is>
       </c>
       <c r="L4" s="35" t="inlineStr">
         <is>
-          <t>2026-11-05</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="M4" s="35" t="inlineStr">
         <is>
-          <t>—（口径校准）</t>
+          <t>$100–150K/年（毛利率修复 3–4pct × 年化约 $4.7M）</t>
         </is>
       </c>
       <c r="N4" s="35" t="inlineStr">
@@ -2474,11 +2824,11 @@
       </c>
       <c r="O4" s="35" t="inlineStr">
         <is>
-          <t>本品类最大的待核事实，影响后续所有结论</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="90" customHeight="1" s="33">
+          <t>主口径改为利润表；V2.9 基线品类范围与利润表不一致</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="160" customHeight="1" s="33">
       <c r="A5" s="4" t="n">
         <v>2</v>
       </c>
@@ -2500,27 +2850,27 @@
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="35" t="inlineStr">
         <is>
-          <t>部分属实</t>
+          <t>属实</t>
         </is>
       </c>
       <c r="G5" s="35" t="inlineStr">
         <is>
-          <t>V1 称 62 个 ASIN 中 31 个负毛利、合计亏损 $239,679；V2.9 品类整体毛利率 16.31%，负毛利 ASIN 数需按 V2.9 ASIN 级数据重算。</t>
+          <t>利润表（领星利润报表-MSKU，2026-01-01~10-24）：91 个 ASIN 中 44 个负毛利（48.4%），负毛利 ASIN 销售额 $1,349,410（占品线 35.1%），合计亏损 $71,061。</t>
         </is>
       </c>
       <c r="H5" s="35" t="inlineStr">
         <is>
-          <t>待按 V2.9 重算；若基线成立，负毛利 SKU 数应明显少于 31 个。</t>
+          <t>结论成立，但亏损额小于 V1（V1：31/62、亏 $239,679）。</t>
         </is>
       </c>
       <c r="I5" s="35" t="inlineStr">
         <is>
-          <t>200W 以下同质款靠降价+高广告维持排名；350W 新品广告费率 46–52% 未形成自然流量。</t>
+          <t>最大亏损款 B0CQ4PFGH5（米沃奇 200W Ecarke，销售 $229K、亏 $14.3K、广告 26.0%）；B0CQ2MHKJ5（得伟 200W LIVOWALNY，$382K、GM −0.7%）、B0CQ2JJ51T（米沃奇 200W，$289K、GM −1.9%）都是 TOP5 款。</t>
         </is>
       </c>
       <c r="J5" s="35" t="inlineStr">
         <is>
-          <t>负毛利 ASIN 分三类处理：①可提价/降本 ②停广告保本 ③清货下架；负毛利 ASIN 暂停新增备货。</t>
+          <t>负毛利 ASIN 分三类：①TOP 款（B0CQ2MHKJ5 / B0CQ2JJ51T / B0CQ4PFGH5）降广告到保本并提价 $1–2；②小款停广告保本；③零销售/长尾清货下架。负毛利 ASIN 暂停新增备货。</t>
         </is>
       </c>
       <c r="K5" s="35" t="inlineStr">
@@ -2535,7 +2885,7 @@
       </c>
       <c r="M5" s="35" t="inlineStr">
         <is>
-          <t>$60–120K/年（按 V1 年化亏损 $360K 的 1/6–1/3 估算）</t>
+          <t>$50–70K/年（扭亏 44 个 ASIN 的年化亏损约 $87K 的 60–80%）</t>
         </is>
       </c>
       <c r="N5" s="35" t="inlineStr">
@@ -2549,7 +2899,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="132" customHeight="1" s="33">
+    <row r="6" ht="174" customHeight="1" s="33">
       <c r="A6" s="4" t="n">
         <v>3</v>
       </c>
@@ -2576,22 +2926,22 @@
       </c>
       <c r="G6" s="35" t="inlineStr">
         <is>
-          <t>「power inverter」2026-09 月搜索 4.48 万、PPC 建议竞价 $1.46、购买率 2.55%、均价 $55.98（卖家精灵 ABA 月度搜索趋势（US，截至 2026-09））。CPC 不贵，高费率主要来自转化率低。</t>
+          <t>利润表（领星利润报表-MSKU，2026-01-01~10-24）：广告费率 &gt;25% 的 ASIN 共 21 个，覆盖销售额 $1,086,390；品类广告费率 17.30%，比公司高 2.48pct。核心词「power inverter」PPC 建议竞价 $1.46、购买率 2.55%（卖家精灵 ABA 月度搜索趋势（US，截至 2026-09））。</t>
         </is>
       </c>
       <c r="H6" s="35" t="inlineStr">
         <is>
-          <t>V2.9 品类整体广告费率 13.99%；超 25% 的 8 个 ASIN 需逐个对照保本 ACOS 复核。</t>
+          <t>比 V1（8 个 ASIN &gt;25%）范围更大。</t>
         </is>
       </c>
       <c r="I6" s="35" t="inlineStr">
         <is>
-          <t>350W/双向 65W 新品评论少、转化弱，靠 SP 宽泛词硬推。</t>
+          <t>CPC 不贵，高费率来自转化率低；200W 同质款靠广告维持排名。</t>
         </is>
       </c>
       <c r="J6" s="35" t="inlineStr">
         <is>
-          <t>8 个 ASIN 设 ACOS 上限 = 保本 ACOS；新品冷启动期上限 35%，60 天未达标预算减半；重做否词与精准词。</t>
+          <t>21 个 ASIN 设 ACOS 上限 = 保本 ACOS；新品冷启动期上限 35%，60 天未达标预算减半；重做否词与精准词。</t>
         </is>
       </c>
       <c r="K6" s="35" t="inlineStr">
@@ -2606,7 +2956,7 @@
       </c>
       <c r="M6" s="35" t="inlineStr">
         <is>
-          <t>$50–75K/年（回收 V1 测算 $150K 低效支出的 1/3–1/2）</t>
+          <t>$60–90K/年（品类广告费率降到 15%）</t>
         </is>
       </c>
       <c r="N6" s="35" t="inlineStr">
@@ -2620,7 +2970,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="118" customHeight="1" s="33">
+    <row r="7" ht="202" customHeight="1" s="33">
       <c r="A7" s="4" t="n">
         <v>4</v>
       </c>
@@ -2647,22 +2997,22 @@
       </c>
       <c r="G7" s="35" t="inlineStr">
         <is>
-          <t>美国站「power inverter」搜索 8 月 3.54 万（同比 −56.6%）、9 月 4.48 万（同比 −19.1%），美国需求在 Q3 明显走弱（卖家精灵 ABA 月度搜索趋势（US，截至 2026-09））。</t>
+          <t>利润表（领星利润报表-MSKU，2026-01-01~10-24）：美国 91.2%（GM 7.8%、广告 17.7%）；加拿大 8.4%（GM 12.7%、广告 13.8%）；墨西哥 0.4%（GM 26.2%、无广告，仅 $15K）；只覆盖 4 个国家。美国「power inverter」搜索 8 月同比 −56.6%、9 月 −19.1%（卖家精灵 ABA 月度搜索趋势（US，截至 2026-09））。</t>
         </is>
       </c>
       <c r="H7" s="35" t="inlineStr">
         <is>
-          <t>加拿大 GM 17.03%（V1）；需用 V2.9 分站点毛利复核美国站 −0.33%。</t>
+          <t>美国站毛利率修正为 7.8%（V1 −0.33%）；加拿大毛利率 12.7%（V1 17.03%）。</t>
         </is>
       </c>
       <c r="I7" s="35" t="inlineStr">
         <is>
-          <t>美国站价格战+广告依赖；加拿大竞争弱、广告费率低。</t>
+          <t>美国价格战+广告依赖；欧洲尚未铺货。</t>
         </is>
       </c>
       <c r="J7" s="35" t="inlineStr">
         <is>
-          <t>加拿大补齐 200W–1000W 主力款 FBA 库存，广告预算向加拿大倾斜 10–15%；墨西哥/巴西各测 2–3 款。</t>
+          <t>加拿大补齐主力款库存，预算倾斜 10–15%；墨西哥扩到 5–8 款；评估德国（同平台电池款）上架。</t>
         </is>
       </c>
       <c r="K7" s="35" t="inlineStr">
@@ -2677,7 +3027,7 @@
       </c>
       <c r="M7" s="35" t="inlineStr">
         <is>
-          <t>$20–30K 毛利（V1 $58K 机会的 1/3–1/2）</t>
+          <t>$20–30K 毛利</t>
         </is>
       </c>
       <c r="N7" s="35" t="inlineStr">
@@ -2718,22 +3068,22 @@
       </c>
       <c r="G8" s="35" t="inlineStr">
         <is>
-          <t>26 年新品 11 个 ASIN 收入 $179,520，ASP $51.13；市场核心词均价 $55.98（卖家精灵 ABA 月度搜索趋势（US，截至 2026-09）），$50+ 价格带有需求。</t>
+          <t>利润表（领星利润报表-MSKU，2026-01-01~10-24）：带「26新品」标签的 7 个 ASIN 只占销售额 4.0%，毛利率 −12.3%、广告费率 24.6%；老品毛利率 9.2%。</t>
         </is>
       </c>
       <c r="H8" s="35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>比 V1 更差（V1 新品占 4.19%、未给毛利）：新品不仅没接棒，还在亏。</t>
         </is>
       </c>
       <c r="I8" s="35" t="inlineStr">
         <is>
-          <t>新品集中在 300–350W，与老品价格带重叠；缺少纯正弦波 1000W+、带 PD 100W 的差异化款。</t>
+          <t>新品集中在 300–350W（350W GM −12.3%、300W GM −8.6%），与老品价格带重叠、无差异化。</t>
         </is>
       </c>
       <c r="J8" s="35" t="inlineStr">
         <is>
-          <t>27 年新品聚焦纯正弦 500–2000W + PD 100W + 显示屏；每款立项前测算保本 ACOS 与认证成本。</t>
+          <t>停止 300–350W 修正波新品投放；27 年新品聚焦 550W+ / 纯正弦 + PD 100W，参考 550W 段（ASP $107.4、GM 17.6%）。</t>
         </is>
       </c>
       <c r="K8" s="35" t="inlineStr">
@@ -2748,7 +3098,7 @@
       </c>
       <c r="M8" s="35" t="inlineStr">
         <is>
-          <t>—（增量见 B1）</t>
+          <t>$20–30K/年（新品止损）</t>
         </is>
       </c>
       <c r="N8" s="35" t="inlineStr">
@@ -2784,27 +3134,27 @@
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="35" t="inlineStr">
         <is>
-          <t>部分属实</t>
+          <t>属实</t>
         </is>
       </c>
       <c r="G9" s="35" t="inlineStr">
         <is>
-          <t>美国「power inverter」全年搜索高峰在 12 月（2025-12 为 22.8 万、2026-01 为 12.4 万，是平月 3–4 倍）；7–9 月不是需求旺季，8 月搜索同比 −56.6%（卖家精灵 ABA 月度搜索趋势（US，截至 2026-09））。</t>
+          <t>领星 ASIN 日报（同期）：6 月 $457K 为年中峰值 → 9 月 $215K（−53%）；10 月 1–24 日 $233K，日均 $9.7K，比 9 月日均 $7.2K 回升 35%。1 月单月 $1,023K（圣诞/年货尾单）为全年最高。</t>
         </is>
       </c>
       <c r="H9" s="35" t="inlineStr">
         <is>
-          <t>「全年约 $6.4M」需重估：V2.9 口径 2–9 月已达 $4.95M，Q4 若接住 12 月峰值，全年可能高于 $6.4M。</t>
+          <t>Q4 反弹已开始；1 月 $1.02M 说明 12–1 月才是真正旺季，「全年约 $6.4M」需按利润表口径重估（1–10/24 已 $3.84M）。</t>
         </is>
       </c>
       <c r="I9" s="35" t="inlineStr">
         <is>
-          <t>季节性判断偏差：把 6 月当峰值，实际黑五/圣诞（车载礼品、冬季备电）才是峰值；Q3 下滑有外部需求因素。</t>
+          <t>季节性判断偏差：6 月不是峰值，12–1 月才是；ABA 显示 2025-12 搜索 22.8 万，是平月 3–4 倍。</t>
         </is>
       </c>
       <c r="J9" s="35" t="inlineStr">
         <is>
-          <t>11–12 月备货与广告预案：提前 4 周提预算，主推 Top5 正毛利 ASIN；12 月库存覆盖 ≥45 天。</t>
+          <t>11–1 月备货与广告预案：提前 4 周提预算，主推正毛利款（550W、利优比 200W B0DHZSTBSD，GM 24.4%）；12 月库存覆盖 ≥45 天。</t>
         </is>
       </c>
       <c r="K9" s="35" t="inlineStr">
@@ -2840,28 +3190,28 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="48" customHeight="1" s="33">
+    <row r="11" ht="76" customHeight="1" s="33">
       <c r="A11" s="8" t="n">
         <v>7</v>
       </c>
       <c r="B11" s="36" t="inlineStr">
         <is>
-          <t>Q4 季节性峰值未纳入计划</t>
+          <t>销售集中在「淘汰」标签链接</t>
         </is>
       </c>
       <c r="C11" s="36" t="inlineStr">
         <is>
-          <t>ABA「power inverter」2025-12 搜索 22.8 万、2026-01 12.4 万，均为平月 3–4 倍</t>
+          <t>利润表（领星利润报表-MSKU，2026-01-01~10-24）：带淘汰标签（含「淘汰-香港店铺替换」「淘汰产品-卖完不卖」）的 77 个 ASIN 贡献 98.2% 销售额；TOP1 B0CQ4Q6WB9（$498K、GM 1.4%）即为此类</t>
         </is>
       </c>
       <c r="D11" s="36" t="inlineStr">
         <is>
-          <t>若 Q4 断货或预算不足，错失全年最大流量窗口</t>
+          <t>若新店铺/新链接承接不顺，可能重演油泵 8 月主链接替换后的断崖</t>
         </is>
       </c>
       <c r="E11" s="36" t="inlineStr">
         <is>
-          <t>原报告以 6 月为峰值，未识别 12 月高峰</t>
+          <t>店铺替换与老品淘汰同时进行</t>
         </is>
       </c>
       <c r="F11" s="36" t="inlineStr">
@@ -2871,7 +3221,7 @@
       </c>
       <c r="G11" s="36" t="inlineStr">
         <is>
-          <t>来源：卖家精灵 ABA 月度搜索趋势（US，截至 2026-09）</t>
+          <t>来源：利润表（领星利润报表-MSKU，2026-01-01~10-24）</t>
         </is>
       </c>
       <c r="H11" s="36" t="inlineStr">
@@ -2881,32 +3231,32 @@
       </c>
       <c r="I11" s="36" t="inlineStr">
         <is>
-          <t>车载礼品+冬季备电需求</t>
+          <t>缺少替换期流量迁移方案</t>
         </is>
       </c>
       <c r="J11" s="36" t="inlineStr">
         <is>
-          <t>按 12 月峰值倒排备货与预算；12 月库存覆盖 ≥45 天</t>
+          <t>列出替换时间表；新链接提前 30 天养评论与广告，旧链接库存清完再切</t>
         </is>
       </c>
       <c r="K11" s="36" t="inlineStr">
         <is>
-          <t>计划 / 运营</t>
+          <t>运营总监</t>
         </is>
       </c>
       <c r="L11" s="36" t="inlineStr">
         <is>
-          <t>2026-11-10</t>
+          <t>2026-11-30</t>
         </is>
       </c>
       <c r="M11" s="36" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>防止断崖</t>
         </is>
       </c>
       <c r="N11" s="36" t="inlineStr">
         <is>
-          <t>进行中</t>
+          <t>待启动</t>
         </is>
       </c>
       <c r="O11" s="36" t="inlineStr">
@@ -2934,8 +3284,6 @@
       <c r="N12" s="9" t="n"/>
       <c r="O12" s="9" t="n"/>
     </row>
-    <row r="13"/>
-    <row r="14"/>
     <row r="15" ht="24" customHeight="1" s="33">
       <c r="A15" s="2" t="inlineStr">
         <is>
@@ -2950,7 +3298,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18" ht="24" customHeight="1" s="33">
       <c r="A18" s="11" t="inlineStr">
         <is>
@@ -3460,8 +3807,6 @@
       <c r="N28" s="9" t="n"/>
       <c r="O28" s="9" t="n"/>
     </row>
-    <row r="29"/>
-    <row r="30"/>
     <row r="31" ht="24" customHeight="1" s="33">
       <c r="A31" s="13" t="inlineStr">
         <is>
@@ -3536,7 +3881,7 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="64" customHeight="1" s="33">
+    <row r="33" ht="76" customHeight="1" s="33">
       <c r="A33" s="4" t="n">
         <v>1</v>
       </c>
@@ -3567,7 +3912,7 @@
       </c>
       <c r="G33" s="35" t="inlineStr">
         <is>
-          <t>按 V2.9 口径重算美国站毛利率（V1 −0.33% 与 V2.9 品类 16.31% 冲突）</t>
+          <t>利润表（领星利润报表-MSKU，2026-01-01~10-24）：美国站 GM 7.8%、广告 17.7%，占品线 91.2%</t>
         </is>
       </c>
       <c r="H33" s="35" t="inlineStr">
@@ -3577,7 +3922,7 @@
       </c>
       <c r="I33" s="35" t="inlineStr">
         <is>
-          <t>数据组口径支持</t>
+          <t>广告组</t>
         </is>
       </c>
       <c r="J33" s="35" t="inlineStr">
@@ -3597,7 +3942,7 @@
       </c>
       <c r="M33" s="35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>V1 的 −0.33% 修正为 7.8%</t>
         </is>
       </c>
     </row>
@@ -3731,7 +4076,7 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="64" customHeight="1" s="33">
+    <row r="36" ht="76" customHeight="1" s="33">
       <c r="A36" s="4" t="n">
         <v>4</v>
       </c>
@@ -3762,7 +4107,7 @@
       </c>
       <c r="G36" s="35" t="inlineStr">
         <is>
-          <t>200W 及以下 Top50 价格分布、CPC 与我司排名</t>
+          <t>利润表（领星利润报表-MSKU，2026-01-01~10-24）：200W 段占 78.1%、毛利率 9.3%、广告 17.7%、ASP $31.6</t>
         </is>
       </c>
       <c r="H36" s="35" t="inlineStr">
@@ -4101,8 +4446,6 @@
       <c r="N43" s="9" t="n"/>
       <c r="O43" s="9" t="n"/>
     </row>
-    <row r="44"/>
-    <row r="45"/>
     <row r="46" ht="24" customHeight="1" s="33">
       <c r="A46" s="15" t="inlineStr">
         <is>
@@ -4120,9 +4463,9 @@
     <row r="48" ht="56" customHeight="1" s="33">
       <c r="A48" s="38" t="inlineStr">
         <is>
-          <t>1）毛利率口径：V1 为 0.44%、V2.9 基线为 16.31%，差 15.9pct，必须先统一口径再定品类策略；
-2）季节性：ABA 显示 12 月是全年搜索峰值（22.8 万），7–9 月下滑部分是需求因素（8 月搜索同比 −56.6%），并非全是我司问题；
-3）合规覆盖率：105 个在售 ASIN 中 UL 458/2743 报告覆盖情况未知，决定 27 年在售 SKU 池。</t>
+          <t>1）真实毛利率：利润表口径 8.32%（V1 0.44%、V2.9 16.31% 均不准），44/91 个 ASIN 负毛利，负毛利 ASIN 占销售额 35.1%；
+2）季节性：1 月单月 $1.02M、10 月日均比 9 月回升 35%，12–1 月才是旺季；
+3）链接安全：98.2% 销售额在带淘汰标签的链接上，店铺替换的承接方案需要补齐。</t>
         </is>
       </c>
       <c r="B48" s="39" t="n"/>
@@ -4140,7 +4483,6 @@
       <c r="N48" s="39" t="n"/>
       <c r="O48" s="40" t="n"/>
     </row>
-    <row r="49"/>
     <row r="50" ht="22" customHeight="1" s="33">
       <c r="A50" s="16" t="inlineStr">
         <is>
@@ -4151,8 +4493,8 @@
     <row r="51" ht="40" customHeight="1" s="33">
       <c r="A51" s="38" t="inlineStr">
         <is>
-          <t>建议：27 年销售额以 V2.9 口径为基数（2–9 月 $4.95M，年化约 $7.4M），目标设 $7.5–8.0M（持平到 +8%），毛利率目标 ≥16%。
-理由：美国站需求 Q3 走弱、200W 段价格战，不宜追量；增量来自纯正弦大功率新品+加拿大，利润优先。口径确认后再最终定值。</t>
+          <t>建议：27 年销售额 $4.5–5.0M（利润表 1–10/24 为 $3.84M，年化约 $4.7M），毛利率目标从 8.3% 提到 ≥12%，广告费率 ≤15%。
+理由：200W 段价格战、负毛利 ASIN 近半，先修利润不追量；增量来自 550W+ 利润款、加拿大/墨西哥和 12–1 月旺季。</t>
         </is>
       </c>
       <c r="B51" s="39" t="n"/>
@@ -4170,7 +4512,6 @@
       <c r="N51" s="39" t="n"/>
       <c r="O51" s="40" t="n"/>
     </row>
-    <row r="52"/>
     <row r="53" ht="22" customHeight="1" s="33">
       <c r="A53" s="16" t="inlineStr">
         <is>
@@ -4200,7 +4541,6 @@
       <c r="N54" s="39" t="n"/>
       <c r="O54" s="40" t="n"/>
     </row>
-    <row r="55"/>
     <row r="56" ht="22" customHeight="1" s="33">
       <c r="A56" s="16" t="inlineStr">
         <is>
@@ -4233,7 +4573,6 @@
       <c r="N57" s="39" t="n"/>
       <c r="O57" s="40" t="n"/>
     </row>
-    <row r="58"/>
     <row r="59" ht="22" customHeight="1" s="33">
       <c r="A59" s="16" t="inlineStr">
         <is>
@@ -4244,8 +4583,8 @@
     <row r="60" ht="40" customHeight="1" s="33">
       <c r="A60" s="38" t="inlineStr">
         <is>
-          <t>渠道：加拿大加深库存与预算，TikTok 小规模试点；价格带：退出 200W 以下低价竞争，主攻 $50–150；
-品牌：以「认证+质保+纯正弦」建立中高端心智；运营：Q4 按 12 月峰值做备货与大促预案。</t>
+          <t>渠道：加拿大加深库存与预算，墨西哥扩款，评估德国；TikTok 小规模试点；价格带：退出 300–350W 修正波，主攻 550W+（ASP $100+）；
+品牌：以「认证+质保+纯正弦」建立中高端心智；运营：12–1 月按旺季备货，店铺替换先养新链接。</t>
         </is>
       </c>
       <c r="B60" s="39" t="n"/>
@@ -4427,7 +4766,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="132" customHeight="1" s="33">
+    <row r="4" ht="216" customHeight="1" s="33">
       <c r="A4" s="4" t="n">
         <v>1</v>
       </c>
@@ -4454,12 +4793,12 @@
       </c>
       <c r="G4" s="35" t="inlineStr">
         <is>
-          <t>月度复盘：3 月 ACOS 15.1%/毛利率 25.9% → 10 月 ACOS 35.9%/毛利率 11.4%；TACOS 7.8% → 15.8%；8 月起 ACOS 连续三个月高于保本（30.4/33.6/35.9% vs 24.7/26.7/27.3%）。</t>
+          <t>利润表（领星利润报表-MSKU，2026-01-01~10-24）：品类毛利率 25.43%（公司 13.77%），广告费率 10.80%，均为七品类最优。月度复盘：3 月 ACOS 15.1%/毛利率 25.9% → 10 月 ACOS 35.9%/毛利率 11.4%；TACOS 7.8% → 15.8%；8 月起 ACOS 连续三个月高于保本（30.4/33.6/35.9% vs 24.7/26.7/27.3%）。</t>
         </is>
       </c>
       <c r="H4" s="35" t="inlineStr">
         <is>
-          <t>起点口径不同（V1 用 2 月 41.5%，复盘以放量首月 3 月 25.9% 为基准），方向一致：3→10 月毛利率下降约 14.5pct。来源：油泵品线月度复盘（领星 ASIN 表现，2025-08-01~2026-10-22）</t>
+          <t>全期毛利率 25.43% 与 V1 的 24.97% 一致；下滑集中在 7 月以后（复盘 3→10 月下降约 14.5pct）。来源：利润表（领星利润报表-MSKU，2026-01-01~10-24）；油泵品线月度复盘（领星 ASIN 表现，2025-08-01~2026-10-22）</t>
         </is>
       </c>
       <c r="I4" s="35" t="inlineStr">
@@ -4498,7 +4837,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="202" customHeight="1" s="33">
+    <row r="5" ht="188" customHeight="1" s="33">
       <c r="A5" s="4" t="n">
         <v>2</v>
       </c>
@@ -4525,12 +4864,12 @@
       </c>
       <c r="G5" s="35" t="inlineStr">
         <is>
-          <t>复盘：6 月峰值 $22.6 万；8 月 −20.4%；9 月 $16.5 万；10 月 1–22 日 $10.4 万，日均 $4,734，比 9 月日均 $5,503 再降 14%。外部需求没有降：「fuel transfer pump」2026 年 1–9 月搜索 80.2 万，同比 +39.6%，9 月同比 +12.6%（卖家精灵 ABA 月度搜索趋势（US，截至 2026-09））。</t>
+          <t>领星 ASIN 日报（同期）：6 月 $344K 为峰值 → 9 月 $207K（−39.8%）；10 月 1–24 日 $129K，日均 $5.4K，比 9 月日均 $6.9K 再降 22%。外部需求没有降：「fuel transfer pump」2026 年 1–9 月搜索 80.2 万，同比 +39.6%（卖家精灵 ABA 月度搜索趋势（US，截至 2026-09））。</t>
         </is>
       </c>
       <c r="H5" s="35" t="inlineStr">
         <is>
-          <t>V1 写 7 月峰值 $380,624，复盘为 6 月 $22.6 万，ASIN 范围不同需对齐；「下滑是内部原因、不是市场萎缩」的结论成立。</t>
+          <t>峰值月修正为 6 月（V1 写 7 月 $380,624）；复盘口径（$22.6 万）比利润表小，是因为复盘扣除了淘汰标签部分。「下滑是内部原因、不是市场萎缩」的结论成立。</t>
         </is>
       </c>
       <c r="I5" s="35" t="inlineStr">
@@ -4569,7 +4908,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="146" customHeight="1" s="33">
+    <row r="6" ht="188" customHeight="1" s="33">
       <c r="A6" s="4" t="n">
         <v>3</v>
       </c>
@@ -4596,12 +4935,12 @@
       </c>
       <c r="G6" s="35" t="inlineStr">
         <is>
-          <t>复盘：B0HG9L16S7 是主链接替换后的承接链接；另有 7 个 SKU 在 2025-08~2026-10 零销售（RYBZ012H0A01、RYBZ091T0A1、RYBZ121H0A1、RYBZ131H0A1、RYBZ171H0A1、RYBZ181H0A1、RYBZ201H0A1）。</t>
+          <t>利润表（领星利润报表-MSKU，2026-01-01~10-24）：品线共 28 个 ASIN，负毛利 5 个（合计销售 $12,328、亏 $1,491），零销售 1 个；复盘另列 7 个零销售 SKU（RYBZ012H0A01、RYBZ091T0A1、RYBZ121H0A1、RYBZ131H0A1、RYBZ171H0A1、RYBZ181H0A1、RYBZ201H0A1）。</t>
         </is>
       </c>
       <c r="H6" s="35" t="inlineStr">
         <is>
-          <t>「3 个 ASIN 四项指标完全一致」更像父体汇总或店铺替换造成的数据重复，需核实是否同一父体下的变体，可能不是真实冗余。</t>
+          <t>「3 个 ASIN 四项指标完全一致」更像父体汇总或店铺替换造成的数据重复，需核实是否为同一父体变体。</t>
         </is>
       </c>
       <c r="I6" s="35" t="inlineStr">
@@ -4611,7 +4950,7 @@
       </c>
       <c r="J6" s="35" t="inlineStr">
         <is>
-          <t>核实三个 ASIN 的关系；同款合并为变体；7 个零销售 SKU 清库存下架，不单独开广告位。</t>
+          <t>核实三个 ASIN 的关系；同款合并为变体；零销售 SKU 清库存下架，不单独开广告位。</t>
         </is>
       </c>
       <c r="K6" s="35" t="inlineStr">
@@ -4640,7 +4979,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="118" customHeight="1" s="33">
+    <row r="7" ht="174" customHeight="1" s="33">
       <c r="A7" s="4" t="n">
         <v>4</v>
       </c>
@@ -4667,22 +5006,22 @@
       </c>
       <c r="G7" s="35" t="inlineStr">
         <is>
-          <t>复盘：B0GLXXSDXD 全站累计 $47.4 万，占全品线 30.9%；Top5 链接占 2026 年 74.6%；5.0GPM 占 1–9 月销售额 89.6%（3.8GPM 4.4%、3.2GPM 4.1%、卧式 1.9%）。</t>
+          <t>利润表（领星利润报表-MSKU，2026-01-01~10-24）：TOP1 B0FW9V5S3W（3.2GPM 感应自停 DIYTOOLIFZ）$714,884，占 29.8%、GM 28.0%；TOP3 65.8%、TOP5 80.6%、TOP10 92.3%。TOP2 B0GLXXSDXD（5GPM 手动款）$524,129、GM 27.3%。</t>
         </is>
       </c>
       <c r="H7" s="35" t="inlineStr">
         <is>
-          <t>V1 的 TOP1 为 B0FW9V5S3W（$576,977），复盘 TOP1 为 B0GLXXSDXD，两版 ASIN 范围不同，需统一。</t>
+          <t>与 V1 一致（TOP1 同为 B0FW9V5S3W）；集中度比 V1 更高（V1 TOP3 61.67%）。注意 TOP1 标签为「淘汰产品-卖完不卖」，TOP2 已在 8 月店铺替换。</t>
         </is>
       </c>
       <c r="I7" s="35" t="inlineStr">
         <is>
-          <t>规格结构单一，一个规格段占近九成；主链接一出问题全线受挫（8 月已兑现）。</t>
+          <t>TOP1、TOP2 两条主链接都处在淘汰/替换中，带淘汰标签的 6 个 ASIN 占品线 73.5% 销售额。</t>
         </is>
       </c>
       <c r="J7" s="35" t="inlineStr">
         <is>
-          <t>建立 Top 链接风险预案（备用链接、评论迁移、店铺健康监控）；3.2GPM 自动低配款扩量做第二梯队。</t>
+          <t>明确 TOP1 淘汰后的承接款（感应自停 Ecarke B0G648BQ9F，$338K、GM 25.8%）；Top 链接风险预案（备用链接、评论迁移）。</t>
         </is>
       </c>
       <c r="K7" s="35" t="inlineStr">
@@ -4692,7 +5031,7 @@
       </c>
       <c r="L7" s="35" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="M7" s="35" t="inlineStr">
@@ -4702,16 +5041,16 @@
       </c>
       <c r="N7" s="35" t="inlineStr">
         <is>
-          <t>待启动</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="O7" s="35" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="146" customHeight="1" s="33">
+          <t>本品类最大风险</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="188" customHeight="1" s="33">
       <c r="A8" s="4" t="n">
         <v>5</v>
       </c>
@@ -4738,12 +5077,12 @@
       </c>
       <c r="G8" s="35" t="inlineStr">
         <is>
-          <t>复盘 1–9 月：美国 86.7%、加拿大 8.6%、德国 3.0%、法国 1.0%、英国 0.5%。德国 5 月上线，7–9 月 $2.7 万，10 月（22 天）$1.29 万，约为美国日均的 1/4；欧洲 7–9 月合计 $4.14 万、占当季 7.7%，且广告几乎没投。</t>
+          <t>利润表（领星利润报表-MSKU，2026-01-01~10-24）：美国 86.3%（GM 23.6%、广告 11.7%）；加拿大 10.8%（GM 39.4%、广告 3.1%）；德国 1.8%（GM 29.3%）；法国 0.7%、英国 0.3%；共 12 个国家。复盘：德国 5 月上线，7–9 月 $2.7 万，10 月（22 天）$1.29 万，欧洲广告几乎没投。</t>
         </is>
       </c>
       <c r="H8" s="35" t="inlineStr">
         <is>
-          <t>加拿大 7–9 月比 1–3 月 +139%；欧洲已起量，机会成立且比 V1 估计更快。</t>
+          <t>加拿大毛利率 39.4%、广告 3.1%，是全公司最好的站点组合之一；加拿大占比已从 V1 的 12.32% 降到 10.8%，需要补库存。</t>
         </is>
       </c>
       <c r="I8" s="35" t="inlineStr">
@@ -4804,27 +5143,27 @@
       <c r="E9" s="5" t="n"/>
       <c r="F9" s="35" t="inlineStr">
         <is>
-          <t>已变化</t>
+          <t>部分属实</t>
         </is>
       </c>
       <c r="G9" s="35" t="inlineStr">
         <is>
-          <t>复盘：3.2GPM 7–9 月 $4.35 万（比 1–3 月 +975%，自动低配款 SPU07144 5 月上市），9 月 ACOS 26.9%、毛利率 16.1%，10 月毛利 $4,097、毛利率 20.5%，是唯一「低价还能赚钱」的段。真正亏损的是 3.8GPM：9 月 ACOS 53.6%、毛利率 −18.4%、毛利 −$4,095，保本 ACOS 仅 −0.5%。</t>
+          <t>利润表（领星利润报表-MSKU，2026-01-01~10-24）：品线负毛利 5 个 ASIN 中，B0H2XJ1NGJ、B0H2XR6HN6 为「手提自动款 3.2GPM（低配 实际 3.8GPM）」，手提自动款整段 6 个 ASIN 销售 $62K、GM 10.2%。复盘：3.8GPM 9 月 ACOS 53.6%、毛利率 −18.4%、毛利 −$4,095。</t>
         </is>
       </c>
       <c r="H9" s="35" t="inlineStr">
         <is>
-          <t>失血段应从「3.2GPM」修正为「3.8GPM（SPU07147）」：8–10 月连续三个月毛利为负。</t>
+          <t>失血款应定位为「手提自动款低配（实际 3.8GPM，SPU07147）」，不是 3.2GPM 感应自停（TOP1，GM 28.0%）。</t>
         </is>
       </c>
       <c r="I9" s="35" t="inlineStr">
         <is>
-          <t>3.8GPM 是定价与成本结构问题（10 月客单价从 $51.7 掉到 $40.2），不投广告也亏。</t>
+          <t>低配款定价与成本结构问题（10 月客单价从 $51.7 掉到 $40.2），不投广告也亏。</t>
         </is>
       </c>
       <c r="J9" s="35" t="inlineStr">
         <is>
-          <t>3.8GPM 停广告并重新定价/降本，做不到就清货；3.2GPM 自动低配款适度加投。</t>
+          <t>低配 3.8GPM 停广告并重新定价/降本，做不到就清货；3.2GPM 自动低配款（SPU07144，复盘 10 月 GM 20.5%）适度加投。</t>
         </is>
       </c>
       <c r="K9" s="35" t="inlineStr">
@@ -4944,8 +5283,6 @@
       <c r="D12" s="9" t="n"/>
       <c r="E12" s="9" t="n"/>
     </row>
-    <row r="13"/>
-    <row r="14"/>
     <row r="15" ht="24" customHeight="1" s="33">
       <c r="A15" s="2" t="inlineStr">
         <is>
@@ -4960,7 +5297,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18" ht="24" customHeight="1" s="33">
       <c r="A18" s="11" t="inlineStr">
         <is>
@@ -5450,8 +5786,6 @@
       <c r="D28" s="9" t="n"/>
       <c r="E28" s="9" t="n"/>
     </row>
-    <row r="29"/>
-    <row r="30"/>
     <row r="31" ht="24" customHeight="1" s="33">
       <c r="A31" s="13" t="inlineStr">
         <is>
@@ -6136,8 +6470,6 @@
       <c r="D44" s="9" t="n"/>
       <c r="E44" s="9" t="n"/>
     </row>
-    <row r="45"/>
-    <row r="46"/>
     <row r="47" ht="24" customHeight="1" s="33">
       <c r="A47" s="15" t="inlineStr">
         <is>
@@ -6155,9 +6487,9 @@
     <row r="49" ht="56" customHeight="1" s="33">
       <c r="A49" s="38" t="inlineStr">
         <is>
-          <t>1）口径：V1 与月度复盘的 TOP1 链接、峰值月份不一致（V1：B0FW9V5S3W、7 月 $380,624；复盘：B0GLXXSDXD、6 月 $22.6 万），需统一 ASIN 范围；
-2）新链接承接：B0HG9L16S7 / B0H1GBF95S 的评论、评分、排名是否接上了主链接，决定 Q4 和 27 年基数；
-3）3.8GPM 成本结构：保本 ACOS 仅 −0.5%，需要采购给出降本空间，才能决定留还是清。</t>
+          <t>1）链接安全：TOP1 B0FW9V5S3W（占 29.8%）标为「淘汰产品-卖完不卖」，TOP2 B0GLXXSDXD 8 月已店铺替换，淘汰标签 ASIN 占 73.5% 销售额，承接方案决定 27 年基数；
+2）口径：复盘（扣除淘汰部分，1–9 月 $120.1 万）与利润表（全量 $2.40M）差一倍，27 年目标要说明用哪个口径；
+3）低配 3.8GPM 成本结构：需采购给出降本空间，才能决定留还是清。</t>
         </is>
       </c>
       <c r="B49" s="39" t="n"/>
@@ -6175,7 +6507,6 @@
       <c r="N49" s="39" t="n"/>
       <c r="O49" s="40" t="n"/>
     </row>
-    <row r="50"/>
     <row r="51" ht="22" customHeight="1" s="33">
       <c r="A51" s="16" t="inlineStr">
         <is>
@@ -6186,8 +6517,8 @@
     <row r="52" ht="40" customHeight="1" s="33">
       <c r="A52" s="38" t="inlineStr">
         <is>
-          <t>建议下调：27 年销售额目标从 $5.05M 调到 $3.5–4.0M，毛利率目标 ≥20%。
-理由：V2.9 口径 2–9 月 $2.395M（年化约 $3.6M），但 10 月日均比 9 月再降 14%；市场搜索 +39.6% 说明有上行空间，前提是先修好链接承接和广告效率。修复达成后（Q1 复盘）再评估上调。</t>
+          <t>建议下调：27 年销售额目标从 $5.05M 调到 $3.3–3.8M，毛利率目标 ≥22%。
+理由：利润表 1–10/24 为 $2.40M（年化约 $2.95M），10 月日均比 9 月再降 22%；市场搜索 +39.6% 有上行空间，前提是两条主链接的流量接回、广告回到保本线以内。Q1 复盘达标后再上调。</t>
         </is>
       </c>
       <c r="B52" s="39" t="n"/>
@@ -6205,7 +6536,6 @@
       <c r="N52" s="39" t="n"/>
       <c r="O52" s="40" t="n"/>
     </row>
-    <row r="53"/>
     <row r="54" ht="22" customHeight="1" s="33">
       <c r="A54" s="16" t="inlineStr">
         <is>
@@ -6235,7 +6565,6 @@
       <c r="N55" s="39" t="n"/>
       <c r="O55" s="40" t="n"/>
     </row>
-    <row r="56"/>
     <row r="57" ht="22" customHeight="1" s="33">
       <c r="A57" s="16" t="inlineStr">
         <is>
@@ -6268,7 +6597,6 @@
       <c r="N58" s="39" t="n"/>
       <c r="O58" s="40" t="n"/>
     </row>
-    <row r="59"/>
     <row r="60" ht="22" customHeight="1" s="33">
       <c r="A60" s="16" t="inlineStr">
         <is>
@@ -6462,7 +6790,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="146" customHeight="1" s="33">
+    <row r="4" ht="160" customHeight="1" s="33">
       <c r="A4" s="4" t="n">
         <v>1</v>
       </c>
@@ -6489,12 +6817,12 @@
       </c>
       <c r="G4" s="35" t="inlineStr">
         <is>
-          <t>看板：1–10 月 18 日新品三兄弟合计 $38.5 万、占 11.6%，毛利率 −0.1% / −1.9% / −7.3%；卧式双供电 3 个型号与 12V+20V 4 个型号均处导入期，合计月均 1,143 台、占 13.6%；卧式双供电 9 月毛利已修复到 17.8%，快充/12V 仍为负。</t>
+          <t>利润表（领星利润报表-MSKU，2026-01-01~10-24）：带「26新品」标签的 28 个 ASIN 占销售额 11.7%，毛利率仅 0.2%、广告费率 22.4%；老品毛利率 14.7%。分形态：双供电 26 气缸 GM 2.9%、快充版 GM −1.5%、12V+20V 手持 GM −1.6%（广告 27.3%）。</t>
         </is>
       </c>
       <c r="H4" s="35" t="inlineStr">
         <is>
-          <t>新品收入占比 11.0%（V1）≈ 11.6%（看板），一致；毛利结论更严重（新品三兄弟毛利均为负）。来源：充气泵品线看板（领星日数据，近60天 08/07–10/05）</t>
+          <t>新品占比 11.0%（V1）≈ 11.7%（利润表），一致；毛利率从 V1 的 3.39% 修正为 0.2%。来源：利润表（领星利润报表-MSKU，2026-01-01~10-24）；充气泵品线看板（领星日数据，近60天 08/07–10/05）</t>
         </is>
       </c>
       <c r="I4" s="35" t="inlineStr">
@@ -6533,7 +6861,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="104" customHeight="1" s="33">
+    <row r="5" ht="188" customHeight="1" s="33">
       <c r="A5" s="4" t="n">
         <v>2</v>
       </c>
@@ -6555,27 +6883,27 @@
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="35" t="inlineStr">
         <is>
-          <t>属实</t>
+          <t>部分属实</t>
         </is>
       </c>
       <c r="G5" s="35" t="inlineStr">
         <is>
-          <t>看板：主力手持高配处于衰退期，得伟/米沃奇/牧田手持高配同比 −49.8% / −24.8% / −53.3%；手持高配 Q1→Q3 −33.6%；衰退期 8 个型号贡献 7–9 月 56.9% 销量。</t>
+          <t>利润表（领星利润报表-MSKU，2026-01-01~10-24）：TOP1 已变为 B0CMH9MT2X（得伟手持高配 LIVOWALNY）$595,470，占 17.8%、GM 15.3%；V1 的 TOP1 B0CMD3CGRN 降为 TOP2（$445,143、13.3%）。TOP3 38.8%、TOP5 47.8%；手持高配版整体占 53.6%、GM 14.9%。</t>
         </is>
       </c>
       <c r="H5" s="35" t="inlineStr">
         <is>
-          <t>集中度风险已在兑现：主力款整体衰退中。</t>
+          <t>单款集中度从 27.37% 修正为 17.8%，但「手持高配」单一形态占一半以上，形态集中风险仍在。</t>
         </is>
       </c>
       <c r="I5" s="35" t="inlineStr">
         <is>
-          <t>手持高配同质化严重，Top6 ASIN 的 CPA $9.7–11.7 高于每单毛利 $2.9–7.2。</t>
+          <t>主力手持高配处于衰退期：看板显示得伟/米沃奇/牧田手持高配同比 −49.8% / −24.8% / −53.3%。</t>
         </is>
       </c>
       <c r="J5" s="35" t="inlineStr">
         <is>
-          <t>手持低价（三平台均处成长期，同比 +23.1% / +30.0% / +46.0%）作为承接梯队；手持高配先修 CPA，不加预算。</t>
+          <t>手持低价（占 14.4%、GM 16.1%、三平台成长期）作为承接梯队；手持高配先修 CPA，不加预算。</t>
         </is>
       </c>
       <c r="K5" s="35" t="inlineStr">
@@ -6604,7 +6932,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="118" customHeight="1" s="33">
+    <row r="6" ht="174" customHeight="1" s="33">
       <c r="A6" s="4" t="n">
         <v>3</v>
       </c>
@@ -6631,7 +6959,7 @@
       </c>
       <c r="G6" s="35" t="inlineStr">
         <is>
-          <t>看板：Q2 $114.8 万 → Q3 $98.8 万（表观 −14%）；6/23–26 Prime Day 四天 $12.2 万，剔除后 Q3 环比仅 −3.8%；6 月 ACOS 30.6%、保本 20.3%、订单毛利率 2.9%。</t>
+          <t>领星 ASIN 日报（同期）：6 月 $419K 为峰值 → 9 月 $307K；10 月 1–24 日 $309K，日均 $12.9K，比 9 月日均 $10.2K 回升 26%。看板：6/23–26 Prime Day 四天 $12.2 万，剔除后 Q3 环比仅 −3.8%；6 月 ACOS 30.6%、保本 20.3%、订单毛利率 2.9%。</t>
         </is>
       </c>
       <c r="H6" s="35" t="inlineStr">
@@ -6675,7 +7003,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="90" customHeight="1" s="33">
+    <row r="7" ht="118" customHeight="1" s="33">
       <c r="A7" s="4" t="n">
         <v>4</v>
       </c>
@@ -6702,12 +7030,12 @@
       </c>
       <c r="G7" s="35" t="inlineStr">
         <is>
-          <t>看板 Q1→Q3：意大利 −64.0%、法国 −32.1%、英国 −24.6%；同期加拿大 +34.5%、德国 +101%。</t>
+          <t>利润表（领星利润报表-MSKU，2026-01-01~10-24）：意大利销售 $8,850（0.3%），GM −4.9%、广告 18.9%。看板 Q1→Q3：意大利 −64.0%、法国 −32.1%、英国 −24.6%。</t>
         </is>
       </c>
       <c r="H7" s="35" t="inlineStr">
         <is>
-          <t>失血不止意大利，英/法/意三站同步下滑。</t>
+          <t>意大利毛利率修正为 −4.9%（V1 −12.11%）；英国反而 GM 25.3%、广告 7.3%，应区别对待。</t>
         </is>
       </c>
       <c r="I7" s="35" t="inlineStr">
@@ -6746,7 +7074,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="90" customHeight="1" s="33">
+    <row r="8" ht="160" customHeight="1" s="33">
       <c r="A8" s="4" t="n">
         <v>5</v>
       </c>
@@ -6773,12 +7101,12 @@
       </c>
       <c r="G8" s="35" t="inlineStr">
         <is>
-          <t>看板：德国 Q1→Q3 +101%，TACOS 9.4%、毛利 14.4%；加拿大 +34.5%，TACOS 15.2%、毛利 9.7%；美国 TACOS 16.8%。</t>
+          <t>利润表（领星利润报表-MSKU，2026-01-01~10-24）：美国 76.5%（GM 11.2%、广告 17.7%）；加拿大 16.7%（GM 17.6%、广告 11.1%）；德国 2.9%（GM 22.7%）；英国 2.2%（GM 25.3%、广告 7.3%）；法国 0.9%（GM 14.7%）。</t>
         </is>
       </c>
       <c r="H8" s="35" t="inlineStr">
         <is>
-          <t>欧洲要分开看：德国是增长点（加投），英法意需先修。</t>
+          <t>欧洲合计约 6.3%（V1 4.61%），德国、英国毛利率都在 22% 以上，扩容机会成立；加拿大占比 16.7% 也明显高于 V1。</t>
         </is>
       </c>
       <c r="I8" s="35" t="inlineStr">
@@ -7045,8 +7373,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
-    <row r="14"/>
     <row r="15" ht="24" customHeight="1" s="33">
       <c r="A15" s="2" t="inlineStr">
         <is>
@@ -7061,7 +7387,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18" ht="24" customHeight="1" s="33">
       <c r="A18" s="11" t="inlineStr">
         <is>
@@ -7607,8 +7932,6 @@
       <c r="D28" s="9" t="n"/>
       <c r="E28" s="9" t="n"/>
     </row>
-    <row r="29"/>
-    <row r="30"/>
     <row r="31" ht="24" customHeight="1" s="33">
       <c r="A31" s="13" t="inlineStr">
         <is>
@@ -8284,8 +8607,6 @@
       <c r="D43" s="9" t="n"/>
       <c r="E43" s="9" t="n"/>
     </row>
-    <row r="44"/>
-    <row r="45"/>
     <row r="46" ht="24" customHeight="1" s="33">
       <c r="A46" s="15" t="inlineStr">
         <is>
@@ -8303,8 +8624,8 @@
     <row r="48" ht="56" customHeight="1" s="33">
       <c r="A48" s="38" t="inlineStr">
         <is>
-          <t>1）主力手持高配衰退（同比 −25% ~ −53%）与手持低价成长（+23% ~ +46%）之后，品类的真实利润结构：低价款 L60 毛利率 15.9% 是最好的利润池；
-2）口径：V1 以 TOP1 B0CMD3CGRN $1,030,074 占 27.37% 推算品类约 $3.76M，V2.9 基线为 $1.57M（44 ASIN），看板为 59 ASIN，三者需统一；
+          <t>1）形态结构：手持高配占 53.6%（GM 14.9%）且在衰退，手持低价占 14.4%（GM 16.1%）在成长，新形态（双供电/快充/12V+20V）毛利 −1.6% ~ 2.9%；
+2）新品：28 个 26 新品 ASIN 毛利率仅 0.2%、广告 22.4%，需要逐款决定留/改/清；
 3）库存与退货：牧田高配周转 376 天、卧式双供电 684 天，牧田退货率 15–16%。</t>
         </is>
       </c>
@@ -8323,7 +8644,6 @@
       <c r="N48" s="39" t="n"/>
       <c r="O48" s="40" t="n"/>
     </row>
-    <row r="49"/>
     <row r="50" ht="22" customHeight="1" s="33">
       <c r="A50" s="16" t="inlineStr">
         <is>
@@ -8334,8 +8654,8 @@
     <row r="51" ht="40" customHeight="1" s="33">
       <c r="A51" s="38" t="inlineStr">
         <is>
-          <t>建议：27 年销售额持平到小幅增长（+0–5%），毛利率目标 ≥13%（V2.9 为 13.2%）。
-理由：市场核心词「tire inflator」1–9 月搜索同比 −2.8%、Q3 −18.2%；主力形态在衰退，增量只能来自手持低价、卧式双供电和德国/加拿大；在 CPA 降到每单毛利以下之前不宜定激进目标。</t>
+          <t>建议：27 年销售额 $4.1–4.3M（利润表 1–10/24 为 $3.34M，年化约 $4.1M，即持平到 +5%），毛利率目标 ≥14%（当前 12.98%）。
+理由：核心词「tire inflator」1–9 月搜索同比 −2.8%、Q3 −18.2%；主力形态在衰退，增量只能来自手持低价、卧式双供电和加拿大/德国/英国；新品毛利 0.2% 在修复前不宜放量。</t>
         </is>
       </c>
       <c r="B51" s="39" t="n"/>
@@ -8353,7 +8673,6 @@
       <c r="N51" s="39" t="n"/>
       <c r="O51" s="40" t="n"/>
     </row>
-    <row r="52"/>
     <row r="53" ht="22" customHeight="1" s="33">
       <c r="A53" s="16" t="inlineStr">
         <is>
@@ -8383,7 +8702,6 @@
       <c r="N54" s="39" t="n"/>
       <c r="O54" s="40" t="n"/>
     </row>
-    <row r="55"/>
     <row r="56" ht="22" customHeight="1" s="33">
       <c r="A56" s="16" t="inlineStr">
         <is>
@@ -8416,7 +8734,6 @@
       <c r="N57" s="39" t="n"/>
       <c r="O57" s="40" t="n"/>
     </row>
-    <row r="58"/>
     <row r="59" ht="22" customHeight="1" s="33">
       <c r="A59" s="16" t="inlineStr">
         <is>
@@ -8611,7 +8928,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="118" customHeight="1" s="33">
+    <row r="4" ht="132" customHeight="1" s="33">
       <c r="A4" s="4" t="n">
         <v>1</v>
       </c>
@@ -8638,27 +8955,27 @@
       </c>
       <c r="G4" s="35" t="inlineStr">
         <is>
-          <t>工作台 V2.9 基线：钉枪 $1,153,080、占公司 4.44%、毛利率 11.22%、广告费率 18.69%（七个品类中最高）、41 个 ASIN。</t>
+          <t>利润表（领星利润报表-MSKU，2026-01-01~10-24）：销售额 $1,710,643（占公司 5.24%），毛利 $201,375（占 4.48%），毛利率 11.77%，比公司 13.77% 低 2.0pct；广告费率 14.82%，与公司持平。</t>
         </is>
       </c>
       <c r="H4" s="35" t="inlineStr">
         <is>
-          <t>毛利率 11.22% 与 V1 一致；广告费率 18.69% 是毛利缺口的主要来源。来源：工作台 V2.9</t>
+          <t>毛利率 11.77%（V1 11.22%），结论成立；广告费率修正为 14.82%（V2.9 18.69%）。按公司毛利率应有约 $236K 毛利，缺口约 $34K（10 个月口径）。</t>
         </is>
       </c>
       <c r="I4" s="35" t="inlineStr">
         <is>
-          <t>高客单但获客成本最高；高价新品线（16GA、T50）毛利偏低。</t>
+          <t>高客单主力款毛利率只有 11.8–13.8%；精加工 16GA 直排 ASP $218.4、GM 仅 3.9%。</t>
         </is>
       </c>
       <c r="J4" s="35" t="inlineStr">
         <is>
-          <t>按 ASIN 设保本 ACOS 上限，品类广告费率目标 ≤14%。</t>
+          <t>16GA 降本或提价；按 ASIN 设保本 ACOS 上限。</t>
         </is>
       </c>
       <c r="K4" s="35" t="inlineStr">
         <is>
-          <t>广告组</t>
+          <t>品类负责人 / 广告组</t>
         </is>
       </c>
       <c r="L4" s="35" t="inlineStr">
@@ -8668,7 +8985,7 @@
       </c>
       <c r="M4" s="35" t="inlineStr">
         <is>
-          <t>$40–80K/年（费率降 4.7pct × 年化约 $1.7M 销售的 1/2–全部）</t>
+          <t>$30–40K/年</t>
         </is>
       </c>
       <c r="N4" s="35" t="inlineStr">
@@ -8682,7 +8999,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="174" customHeight="1" s="33">
+    <row r="5" ht="244" customHeight="1" s="33">
       <c r="A5" s="4" t="n">
         <v>2</v>
       </c>
@@ -8709,12 +9026,12 @@
       </c>
       <c r="G5" s="35" t="inlineStr">
         <is>
-          <t>「cordless nail gun」2026 年 1–9 月搜索 9.78 万，同比 −33.2%，9 月 5,718，同比 −69%（卖家精灵 ABA 月度搜索趋势（US，截至 2026-09））；核心词需求在萎缩，需补拉 brad nailer / finish nailer / framing nailer 等细分词，确认是需求下降还是搜索分流。</t>
+          <t>领星 ASIN 日报（同期）：1 月 $273K → 5 月 $149K → 8 月 $127K；H1 $1,195K，Q3 $405K（比 Q2 $514K 下降 21%）；10 月 1–24 日 $125K，日均 $5.2K，比 9 月日均 $4.5K 回升 15%。「cordless nail gun」2026 年 1–9 月搜索 9.78 万，同比 −33.2%（卖家精灵 ABA 月度搜索趋势（US，截至 2026-09）），需补拉 brad / finish / framing 细分词。</t>
         </is>
       </c>
       <c r="H5" s="35" t="inlineStr">
         <is>
-          <t>H2 下滑有外部需求因素，不全是相对竞争力下降。</t>
+          <t>H2 下滑属实，且有外部需求因素，不全是相对竞争力下降；10 月已企稳。</t>
         </is>
       </c>
       <c r="I5" s="35" t="inlineStr">
@@ -8724,7 +9041,7 @@
       </c>
       <c r="J5" s="35" t="inlineStr">
         <is>
-          <t>补拉细分词数据，按细分（brad / finish / framing）重新分配预算。</t>
+          <t>补拉细分词数据，按细分重新分配预算；Q4 守住 TOP 款排名。</t>
         </is>
       </c>
       <c r="K5" s="35" t="inlineStr">
@@ -8753,7 +9070,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="90" customHeight="1" s="33">
+    <row r="6" ht="132" customHeight="1" s="33">
       <c r="A6" s="4" t="n">
         <v>3</v>
       </c>
@@ -8780,12 +9097,12 @@
       </c>
       <c r="G6" s="35" t="inlineStr">
         <is>
-          <t>TOP1 B0DKXQB75G 为老品，占 31.04%；TOP10 合计 82.20%。</t>
+          <t>利润表（领星利润报表-MSKU，2026-01-01~10-24）：TOP1 B0DKXQB75G（得伟新款大钉枪两用无刷 Mtiolhig）$470,330，占 27.5%、GM 13.1%；TOP3 50.7%、TOP5 64.5%、TOP10 79.1%。</t>
         </is>
       </c>
       <c r="H6" s="35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TOP1 占比修正为 27.5%（V1 31.04%），仍属高集中。</t>
         </is>
       </c>
       <c r="I6" s="35" t="inlineStr">
@@ -8824,7 +9141,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="90" customHeight="1" s="33">
+    <row r="7" ht="188" customHeight="1" s="33">
       <c r="A7" s="4" t="n">
         <v>4</v>
       </c>
@@ -8846,27 +9163,27 @@
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="35" t="inlineStr">
         <is>
-          <t>属实</t>
+          <t>部分属实</t>
         </is>
       </c>
       <c r="G7" s="35" t="inlineStr">
         <is>
-          <t>16GA 线 ASP $213.85 / GM +6.43%；T50 线 ASP $65.85 / GM +2.26% / 广告 23.0%。</t>
+          <t>利润表（领星利润报表-MSKU，2026-01-01~10-24）：精加工钉枪 16GA 直排 5 个 ASIN 占 8.1%，ASP $218.4、GM 3.9%、广告 16.3%；T50 无绳订书机 4 个 ASIN 占 2.6%，GM 6.7%、广告 21.2%；掌上钉枪 GM 6.7%。但带「26新品」标签的 15 个 ASIN 整体 GM 13.6%，高于老品 11.2%。</t>
         </is>
       </c>
       <c r="H7" s="35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>「最贵的线最不赚钱」成立（16GA GM 3.9%，比 V1 的 6.43% 更低）；但新品整体并不亏，问题集中在 16GA 和 T50 两条线。</t>
         </is>
       </c>
       <c r="I7" s="35" t="inlineStr">
         <is>
-          <t>16GA 成本偏高；T50 广告依赖。</t>
+          <t>16GA 采购成本高、与原厂正面竞争；T50 广告依赖。</t>
         </is>
       </c>
       <c r="J7" s="35" t="inlineStr">
         <is>
-          <t>16GA 线降本或提价，目标 GM 12%；T50 线广告费率压到 15%，三个月未达标收缩。</t>
+          <t>16GA 降本或提价，目标 GM 12%；T50 广告费率压到 15%，三个月未达标收缩。</t>
         </is>
       </c>
       <c r="K7" s="35" t="inlineStr">
@@ -8881,7 +9198,7 @@
       </c>
       <c r="M7" s="35" t="inlineStr">
         <is>
-          <t>$20K（V1 测算 $40K 的一半）</t>
+          <t>$15–20K/年</t>
         </is>
       </c>
       <c r="N7" s="35" t="inlineStr">
@@ -8895,7 +9212,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="146" customHeight="1" s="33">
+    <row r="8" ht="230" customHeight="1" s="33">
       <c r="A8" s="4" t="n">
         <v>5</v>
       </c>
@@ -8922,12 +9239,12 @@
       </c>
       <c r="G8" s="35" t="inlineStr">
         <is>
-          <t>重复 SKU：B0H2DW2MPY / B0G6DPPPDC（收入 $86,369、ASP $213.78、GM +6.81%、广告 15.9%）；5 个负毛利 ASIN 合计收入 $44,591、亏损 $3,362；3 个零销售 ASIN。</t>
+          <t>利润表（领星利润报表-MSKU，2026-01-01~10-24）：51 个 ASIN 中负毛利 10 个（合计销售 $83,659、亏 $7,480），零销售 5 个，广告费率 &gt;25% 的 4 个。最大亏损：B0FK2B4X3J（得伟小型两用，亏 $1,362、广告 27.8%）、B0GT91YQ44（T50，亏 $1,288）、B0FDG8WQYF（牧田小钉枪，广告 53.6%）。重复 SKU：B0H2DW2MPY / B0G6DPPPDC（V1）。</t>
         </is>
       </c>
       <c r="H8" s="35" t="inlineStr">
         <is>
-          <t>重复 SKU 需先核实是否为同一父体数据重复。</t>
+          <t>负毛利 ASIN 从 V1 的 5 个修正为 10 个，亏损 $7,480（V1 $3,362）。</t>
         </is>
       </c>
       <c r="I8" s="35" t="inlineStr">
@@ -8952,7 +9269,7 @@
       </c>
       <c r="M8" s="35" t="inlineStr">
         <is>
-          <t>$5–10K</t>
+          <t>$8–12K</t>
         </is>
       </c>
       <c r="N8" s="35" t="inlineStr">
@@ -8966,7 +9283,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="104" customHeight="1" s="33">
+    <row r="9" ht="146" customHeight="1" s="33">
       <c r="A9" s="4" t="n">
         <v>6</v>
       </c>
@@ -8993,12 +9310,12 @@
       </c>
       <c r="G9" s="35" t="inlineStr">
         <is>
-          <t>美国 78.34% / GM 10.59% / 广告 17.1%；加拿大 20.34% / GM 13.07% / 广告 11.1%；德国 GM 20.53% 但只铺了 2 个 ASIN。</t>
+          <t>利润表（领星利润报表-MSKU，2026-01-01~10-24）：美国 79.8%（GM 11.1%、广告 16.2%）；加拿大 18.7%（GM 14.3%、广告 9.3%）；德国 1.3%（GM 19.4%、$22,834）；法国 GM −5.3%、广告 25.1%。</t>
         </is>
       </c>
       <c r="H9" s="35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>与 V1 一致；法国为新增失血点（金额小）。</t>
         </is>
       </c>
       <c r="I9" s="35" t="inlineStr">
@@ -9062,8 +9379,6 @@
       <c r="D12" s="9" t="n"/>
       <c r="E12" s="9" t="n"/>
     </row>
-    <row r="13"/>
-    <row r="14"/>
     <row r="15" ht="24" customHeight="1" s="33">
       <c r="A15" s="2" t="inlineStr">
         <is>
@@ -9078,7 +9393,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18" ht="24" customHeight="1" s="33">
       <c r="A18" s="11" t="inlineStr">
         <is>
@@ -9568,8 +9882,6 @@
       <c r="D28" s="9" t="n"/>
       <c r="E28" s="9" t="n"/>
     </row>
-    <row r="29"/>
-    <row r="30"/>
     <row r="31" ht="24" customHeight="1" s="33">
       <c r="A31" s="13" t="inlineStr">
         <is>
@@ -10254,8 +10566,6 @@
       <c r="D44" s="9" t="n"/>
       <c r="E44" s="9" t="n"/>
     </row>
-    <row r="45"/>
-    <row r="46"/>
     <row r="47" ht="24" customHeight="1" s="33">
       <c r="A47" s="15" t="inlineStr">
         <is>
@@ -10273,9 +10583,9 @@
     <row r="49" ht="56" customHeight="1" s="33">
       <c r="A49" s="38" t="inlineStr">
         <is>
-          <t>1）需求端：核心词「cordless nail gun」1–9 月搜索 −33.2%，需补拉细分词判断是需求萎缩还是搜索分流；
+          <t>1）需求端：核心词「cordless nail gun」1–9 月搜索 −33.2%，Q3 销售额比 Q2 降 21%，10 月日均回升 15%，需判断是需求萎缩还是搜索分流；
 2）安全合规：在售款是否全部为顺序触发、是否存在与 Ridgid 召回同类的风险；
-3）广告效率：品类广告费率 18.69% 为七品类最高，需按 ASIN 拆出高费率来源。</t>
+3）16GA 成本：GM 3.9%，需采购给出降本空间。</t>
         </is>
       </c>
       <c r="B49" s="39" t="n"/>
@@ -10293,7 +10603,6 @@
       <c r="N49" s="39" t="n"/>
       <c r="O49" s="40" t="n"/>
     </row>
-    <row r="50"/>
     <row r="51" ht="22" customHeight="1" s="33">
       <c r="A51" s="16" t="inlineStr">
         <is>
@@ -10304,8 +10613,8 @@
     <row r="52" ht="40" customHeight="1" s="33">
       <c r="A52" s="38" t="inlineStr">
         <is>
-          <t>建议：27 年销售额按持平设定（以 V2.9 年化约 $1.7M 为基数，±5%），毛利率目标从 11.22% 提到 ≥13%。
-理由：核心词需求下行、住宅建筑周期走弱、H2 逆势下滑，不支撑高增长；利润修复靠控广告和 16GA/T50 降本。</t>
+          <t>建议：27 年销售额按持平设定 $2.0–2.2M（利润表 1–10/24 为 $1.71M，年化约 $2.1M），毛利率目标从 11.77% 提到 ≥13%。
+理由：核心词需求下行、住宅建筑周期走弱，不支撑高增长；利润修复靠 16GA/T50 止损和加拿大/德国结构迁移。</t>
         </is>
       </c>
       <c r="B52" s="39" t="n"/>
@@ -10323,7 +10632,6 @@
       <c r="N52" s="39" t="n"/>
       <c r="O52" s="40" t="n"/>
     </row>
-    <row r="53"/>
     <row r="54" ht="22" customHeight="1" s="33">
       <c r="A54" s="16" t="inlineStr">
         <is>
@@ -10353,7 +10661,6 @@
       <c r="N55" s="39" t="n"/>
       <c r="O55" s="40" t="n"/>
     </row>
-    <row r="56"/>
     <row r="57" ht="22" customHeight="1" s="33">
       <c r="A57" s="16" t="inlineStr">
         <is>
@@ -10385,7 +10692,6 @@
       <c r="N58" s="39" t="n"/>
       <c r="O58" s="40" t="n"/>
     </row>
-    <row r="59"/>
     <row r="60" ht="22" customHeight="1" s="33">
       <c r="A60" s="16" t="inlineStr">
         <is>
@@ -10579,7 +10885,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="146" customHeight="1" s="33">
+    <row r="4" ht="244" customHeight="1" s="33">
       <c r="A4" s="4" t="n">
         <v>1</v>
       </c>
@@ -10606,12 +10912,12 @@
       </c>
       <c r="G4" s="35" t="inlineStr">
         <is>
-          <t>「cordless grease gun」2026 年 Q3 搜索 1.26 万，同比 +33.5%（9 月 4,680，同比 +58%）；均价 $99.99、PPC 建议竞价 $3.02（七品类核心词中最高）、购买率 1.82%（卖家精灵 ABA 月度搜索趋势（US，截至 2026-09））。</t>
+          <t>利润表（领星利润报表-MSKU，2026-01-01~10-24）：全期毛利率 18.86%（公司 13.77%），广告费率 16.23%。领星 ASIN 日报（同期）：7 月 $228K 峰值 → 9 月 $129K → 10 月 1–24 日 $103K（日均 $4.3K，与 9 月持平）。市场：「cordless grease gun」Q3 搜索同比 +33.5%，PPC 建议竞价 $3.02（七品类核心词中最高）（卖家精灵 ABA 月度搜索趋势（US，截至 2026-09））。</t>
         </is>
       </c>
       <c r="H4" s="35" t="inlineStr">
         <is>
-          <t>市场在增长，毛利下滑是我司自身问题；高 CPC 放大了广告费率上升。</t>
+          <t>全期毛利率 18.86%，月度下滑趋势（V1）需用月度利润表复核；市场在增长、销售额在跌，是我司自身问题。</t>
         </is>
       </c>
       <c r="I4" s="35" t="inlineStr">
@@ -10677,12 +10983,12 @@
       </c>
       <c r="G5" s="35" t="inlineStr">
         <is>
-          <t>美国：GM 16.84%、广告费率 20.36%，9 月 GM 4.0%；加拿大 GM 30.43%、广告费率 7.07%。</t>
+          <t>利润表（领星利润报表-MSKU，2026-01-01~10-24）：美国 81.2%（GM 16.6%、广告 18.5%）；加拿大 10.6%（GM 28.7%、广告 7.6%）；德国 7.1%（GM 29.1%、广告 4.0%）。</t>
         </is>
       </c>
       <c r="H5" s="35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>美国站占比修正为 81.2%（V1 71.41%），毛利率 16.6% 与 V1 一致；美国广告费率是加拿大的 2.4 倍。</t>
         </is>
       </c>
       <c r="I5" s="35" t="inlineStr">
@@ -10721,7 +11027,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="188" customHeight="1" s="33">
+    <row r="6" ht="216" customHeight="1" s="33">
       <c r="A6" s="4" t="n">
         <v>3</v>
       </c>
@@ -10743,17 +11049,17 @@
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="35" t="inlineStr">
         <is>
-          <t>属实</t>
+          <t>部分属实</t>
         </is>
       </c>
       <c r="G6" s="35" t="inlineStr">
         <is>
-          <t>评论汇总：DIYtoolifz 父体 B0H8NGT4SZ（含 B0FVSBJLDF / B0FVS9SFMJ / B0FVS1VP9F）74 条文字评论中差评 13 条，占全部 26 条差评的 50%；该父体问题集中在做工/塑料箱（6 次）、接头锁不住/滑丝（4 次）、压力不足/气阻（3 次）。来源：黄油枪品线·评论汇总（11 子 ASIN，131 条文字评论，2026-10-20）</t>
+          <t>利润表（领星利润报表-MSKU，2026-01-01~10-24）：带「26新品」标签的 11 个 ASIN 占 36.4%，GM 18.8%，与老品 18.9% 持平；但 B0FVSBJLDF（DIYTOOLIFZ 得伟两用款，$158K）GM 10.7%、广告 23.8%。评论汇总：DIYtoolifz 父体 74 条文字评论中差评 13 条，占全部 26 条差评的 50%，集中在做工/塑料箱、接头锁不住、压力不足。</t>
         </is>
       </c>
       <c r="H6" s="35" t="inlineStr">
         <is>
-          <t>新品负毛利不只是价格/广告问题，还有品质问题拉低转化、增加退货。</t>
+          <t>新品整体并未「集体失血」（全期 GM 18.8%），问题集中在 DIYtoolifz 系列；需用月度数据确认 8–9 月是否转负。</t>
         </is>
       </c>
       <c r="I6" s="35" t="inlineStr">
@@ -10792,7 +11098,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="146" customHeight="1" s="33">
+    <row r="7" ht="174" customHeight="1" s="33">
       <c r="A7" s="4" t="n">
         <v>4</v>
       </c>
@@ -10819,12 +11125,12 @@
       </c>
       <c r="G7" s="35" t="inlineStr">
         <is>
-          <t>TOP1 B0FJ8GLMQD（Ecarke A，黄色 DeWalt 20V）页面评分数 239；Ecarke A 父体 25 条文字评论中差评 7 条（28%），压力不足/气阻 3 次最突出。主力款月收入从 4 月 $104,162 降到 9 月 $41,997（−59.7%）。</t>
+          <t>利润表（领星利润报表-MSKU，2026-01-01~10-24）：TOP1 B0FJ8GLMQD（Ecarke 得伟两用款）$569,822，占 35.0%、GM 23.3%；TOP3 57.8%、TOP5 75.6%、TOP10 99.7%。评论汇总：Ecarke A 父体 25 条文字评论中差评 7 条（28%），压力不足/气阻 3 次最突出。</t>
         </is>
       </c>
       <c r="H7" s="35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TOP1 占比修正为 35.0%（V1 43.76%），仍极高；TOP10 几乎就是整个品类。</t>
         </is>
       </c>
       <c r="I7" s="35" t="inlineStr">
@@ -10863,7 +11169,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="104" customHeight="1" s="33">
+    <row r="8" ht="132" customHeight="1" s="33">
       <c r="A8" s="4" t="n">
         <v>5</v>
       </c>
@@ -10890,12 +11196,12 @@
       </c>
       <c r="G8" s="35" t="inlineStr">
         <is>
-          <t>9 个「黄油枪（二开）」ASIN 2–9 月零销售；2 个配件 ASIN 广告费率 50.03%、毛利率 −6.09%；评论汇总显示配件 0 条差评。</t>
+          <t>利润表（领星利润报表-MSKU，2026-01-01~10-24）：17 个 ASIN 中零销售 5 个（含 6 个「直转 2.0 款」仅 $530）；负毛利 3 个，其中配件耦合器 B0GGQJ2VV8 广告 57.8%、亏 $854；评论汇总显示配件 0 条差评。</t>
         </is>
       </c>
       <c r="H8" s="35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>零销售 ASIN 从 V1 的 9 个修正为 5 个；直转 2.0 款上新未起量，需决定是否继续投入。</t>
         </is>
       </c>
       <c r="I8" s="35" t="inlineStr">
@@ -10934,7 +11240,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="104" customHeight="1" s="33">
+    <row r="9" ht="118" customHeight="1" s="33">
       <c r="A9" s="4" t="n">
         <v>6</v>
       </c>
@@ -10961,7 +11267,7 @@
       </c>
       <c r="G9" s="35" t="inlineStr">
         <is>
-          <t>美国广告费率 20.36% / GM 16.84%；加拿大 7.07% / 30.43%；德国 4.43% / 29.80%，但德国只铺了 2 个 ASIN。</t>
+          <t>利润表（领星利润报表-MSKU，2026-01-01~10-24）：美国广告 18.5% / GM 16.6%；加拿大 7.6% / 28.7%；德国 4.0% / 29.1%，德国已占 7.1%（$116K）。</t>
         </is>
       </c>
       <c r="H9" s="35" t="inlineStr">
@@ -11096,8 +11402,6 @@
       <c r="D12" s="9" t="n"/>
       <c r="E12" s="9" t="n"/>
     </row>
-    <row r="13"/>
-    <row r="14"/>
     <row r="15" ht="24" customHeight="1" s="33">
       <c r="A15" s="2" t="inlineStr">
         <is>
@@ -11112,7 +11416,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18" ht="24" customHeight="1" s="33">
       <c r="A18" s="11" t="inlineStr">
         <is>
@@ -11602,8 +11905,6 @@
       <c r="D28" s="9" t="n"/>
       <c r="E28" s="9" t="n"/>
     </row>
-    <row r="29"/>
-    <row r="30"/>
     <row r="31" ht="24" customHeight="1" s="33">
       <c r="A31" s="13" t="inlineStr">
         <is>
@@ -12223,8 +12524,6 @@
       <c r="D43" s="9" t="n"/>
       <c r="E43" s="9" t="n"/>
     </row>
-    <row r="44"/>
-    <row r="45"/>
     <row r="46" ht="24" customHeight="1" s="33">
       <c r="A46" s="15" t="inlineStr">
         <is>
@@ -12243,8 +12542,8 @@
       <c r="A48" s="38" t="inlineStr">
         <is>
           <t>1）品质：26 条差评中做工、压力/气阻、接头占 43.1%，DIYtoolifz 父体占差评一半，需要退货原因数据交叉验证；
-2）市场：「cordless grease gun」Q3 搜索 +33.5%，市场在涨我司在跌，是内部问题；
-3）口径：V2.9 基线 $843,651，V1 美国站 $945,110 占 71.41%（推算约 $1.32M），需统一。</t>
+2）市场：「cordless grease gun」Q3 搜索 +33.5%，我司 7→9 月销售额 −43%，是内部问题；
+3）月度毛利：利润表全期 GM 18.86%，V1 的「单调下滑到 12.95%」需按月复核，确认是否仍在下滑。</t>
         </is>
       </c>
       <c r="B48" s="39" t="n"/>
@@ -12262,7 +12561,6 @@
       <c r="N48" s="39" t="n"/>
       <c r="O48" s="40" t="n"/>
     </row>
-    <row r="49"/>
     <row r="50" ht="22" customHeight="1" s="33">
       <c r="A50" s="16" t="inlineStr">
         <is>
@@ -12273,8 +12571,8 @@
     <row r="51" ht="40" customHeight="1" s="33">
       <c r="A51" s="38" t="inlineStr">
         <is>
-          <t>建议：27 年销售额按 V2.9 基数持平或 +10%，毛利率目标回到 ≥20%（V2.9 为 13.55%）。
-理由：需求在增长，但当前增长靠降价和广告，品质整改完成前不宜放量；先修毛利与评分，再追量。</t>
+          <t>建议：27 年销售额 $2.0–2.2M（利润表 1–10/24 为 $1.63M，年化约 $2.0M），毛利率目标 ≥21%（当前 18.86%）。
+理由：需求在增长，但 7 月后销售下滑、美国广告费率 18.5%；品质整改完成前不宜放量，先修评分与毛利，再追量。</t>
         </is>
       </c>
       <c r="B51" s="39" t="n"/>
@@ -12292,7 +12590,6 @@
       <c r="N51" s="39" t="n"/>
       <c r="O51" s="40" t="n"/>
     </row>
-    <row r="52"/>
     <row r="53" ht="22" customHeight="1" s="33">
       <c r="A53" s="16" t="inlineStr">
         <is>
@@ -12322,7 +12619,6 @@
       <c r="N54" s="39" t="n"/>
       <c r="O54" s="40" t="n"/>
     </row>
-    <row r="55"/>
     <row r="56" ht="22" customHeight="1" s="33">
       <c r="A56" s="16" t="inlineStr">
         <is>
@@ -12354,7 +12650,6 @@
       <c r="N57" s="39" t="n"/>
       <c r="O57" s="40" t="n"/>
     </row>
-    <row r="58"/>
     <row r="59" ht="22" customHeight="1" s="33">
       <c r="A59" s="16" t="inlineStr">
         <is>
@@ -12548,7 +12843,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="118" customHeight="1" s="33">
+    <row r="4" ht="216" customHeight="1" s="33">
       <c r="A4" s="4" t="n">
         <v>1</v>
       </c>
@@ -12570,42 +12865,42 @@
       <c r="E4" s="5" t="n"/>
       <c r="F4" s="35" t="inlineStr">
         <is>
-          <t>部分属实</t>
+          <t>属实</t>
         </is>
       </c>
       <c r="G4" s="35" t="inlineStr">
         <is>
-          <t>工作台 V2.9 基线：冲击扳手 $438,040、占公司 1.69%、毛利率 5.92%（七个品类中最低）、广告费率 14.7%、21 个 ASIN；与 V1（约 $2.40M、85 个 ASIN、GM 13.48%）差距很大。</t>
+          <t>利润表（领星利润报表-MSKU，2026-01-01~10-24）：1100N 段占 35.4%（ASP $64.3、GM 9.6%、广告 15.3%），900N GM 5.2%、1000N GM −0.7%；1600N 占 34.0%（GM 16.0%）；2200N 占 15.6%（ASP $140.3、GM 23.4%、广告 10.5%）。TOP1 B0CTKFKGL9（1100N）$442K，GM 仅 5.2%。</t>
         </is>
       </c>
       <c r="H4" s="35" t="inlineStr">
         <is>
-          <t>需先确认品类口径（V1 是否把其他扳手/套筒或其他店铺计入）。若以 V2.9 为准，品类毛利率只有 5.92%，扭矩段结构需重算。来源：工作台 V2.9</t>
+          <t>结构倒挂成立：低扭矩段（900–1100N）合计 38.1%、毛利率 &lt;10%；高扭矩 2200N 毛利率 23.4%。V2.9 基线（$438K / 21 ASIN / GM 5.92%）品类范围不完整，以利润表为准。</t>
         </is>
       </c>
       <c r="I4" s="35" t="inlineStr">
         <is>
-          <t>低扭矩段（900–1100N）占比高、毛利低。</t>
+          <t>低扭矩段同质化，白牌价格压制；TOP1 款毛利率只有 5.2%。</t>
         </is>
       </c>
       <c r="J4" s="35" t="inlineStr">
         <is>
-          <t>数据组按 V2.9 ASIN 清单重算扭矩段结构；资源向 2200N+ 倾斜。</t>
+          <t>预算与新品向 1600N / 2200N 倾斜；TOP1 1100N 提价 $2–3 或降本；1000N 段（19 个 ASIN、GM −0.7%）清理。</t>
         </is>
       </c>
       <c r="K4" s="35" t="inlineStr">
         <is>
-          <t>数据分析 / 品类负责人</t>
+          <t>品类负责人</t>
         </is>
       </c>
       <c r="L4" s="35" t="inlineStr">
         <is>
-          <t>2026-11-15</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="M4" s="35" t="inlineStr">
         <is>
-          <t>—（口径校准）</t>
+          <t>$40–60K/年（1100N 段毛利率提 3–5pct）</t>
         </is>
       </c>
       <c r="N4" s="35" t="inlineStr">
@@ -12615,11 +12910,11 @@
       </c>
       <c r="O4" s="35" t="inlineStr">
         <is>
-          <t>本品类最大的待核事实</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="104" customHeight="1" s="33">
+          <t>V1 结论被利润表确认</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="174" customHeight="1" s="33">
       <c r="A5" s="4" t="n">
         <v>2</v>
       </c>
@@ -12641,27 +12936,27 @@
       <c r="E5" s="5" t="n"/>
       <c r="F5" s="35" t="inlineStr">
         <is>
-          <t>部分属实</t>
+          <t>属实</t>
         </is>
       </c>
       <c r="G5" s="35" t="inlineStr">
         <is>
-          <t>V1：美国 85.18% / GM 11.90% / 广告 18.0%；德国 GM 23.42%；加拿大广告 6.7% / GM 18.75%。需用 V2.9 口径复核。</t>
+          <t>利润表（领星利润报表-MSKU，2026-01-01~10-24）：美国 78.0%（GM 13.3%、广告 15.0%）；加拿大 11.6%（GM 14.3%、广告 6.8%）；德国 6.3%（GM 22.1%、$214,865）；法国 2.0%（GM 23.8%）；墨西哥 1.0%（GM 29.1%、无广告）；共 15 个国家。</t>
         </is>
       </c>
       <c r="H5" s="35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>德国、法国毛利率 22–24%，比美国高 9–10pct；结论成立。</t>
         </is>
       </c>
       <c r="I5" s="35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>预算按收入分配，没按毛利效率分配。</t>
         </is>
       </c>
       <c r="J5" s="35" t="inlineStr">
         <is>
-          <t>口径确认后，预算向德国、加拿大倾斜。</t>
+          <t>德国、法国加投 1600N / 2200N；加拿大补库存；墨西哥扩款。</t>
         </is>
       </c>
       <c r="K5" s="35" t="inlineStr">
@@ -12676,7 +12971,7 @@
       </c>
       <c r="M5" s="35" t="inlineStr">
         <is>
-          <t>$10–20K</t>
+          <t>$20–30K 毛利</t>
         </is>
       </c>
       <c r="N5" s="35" t="inlineStr">
@@ -12690,7 +12985,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="90" customHeight="1" s="33">
+    <row r="6" ht="132" customHeight="1" s="33">
       <c r="A6" s="4" t="n">
         <v>3</v>
       </c>
@@ -12712,27 +13007,27 @@
       <c r="E6" s="5" t="n"/>
       <c r="F6" s="35" t="inlineStr">
         <is>
-          <t>部分属实</t>
+          <t>属实</t>
         </is>
       </c>
       <c r="G6" s="35" t="inlineStr">
         <is>
-          <t>V1 为 85 个 ASIN，V2.9 只有 21 个，「加拿大 40 个 ASIN」等结论需复核。</t>
+          <t>利润表（领星利润报表-MSKU，2026-01-01~10-24）：103 个 ASIN，TOP10 占 55.5%（V1 61.47%）；1000N 段 19 个 ASIN 只做出 $23K，900N 段 15 个 ASIN 做出 $70K；零销售 5 个。</t>
         </is>
       </c>
       <c r="H6" s="35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>两极分化成立：长尾 ASIN 多、单 ASIN 产出低。</t>
         </is>
       </c>
       <c r="I6" s="35" t="inlineStr">
         <is>
-          <t>长尾站点铺货多。</t>
+          <t>多站点、多店铺铺货。</t>
         </is>
       </c>
       <c r="J6" s="35" t="inlineStr">
         <is>
-          <t>零产出 ASIN 下架（巴西 19 个仅 $410、波兰 4 个零产出）。</t>
+          <t>1000N / 900N 段合并或下架；长尾站点零产出 ASIN 清理。</t>
         </is>
       </c>
       <c r="K6" s="35" t="inlineStr">
@@ -12747,7 +13042,7 @@
       </c>
       <c r="M6" s="35" t="inlineStr">
         <is>
-          <t>$5K</t>
+          <t>$5–10K</t>
         </is>
       </c>
       <c r="N6" s="35" t="inlineStr">
@@ -12761,7 +13056,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="118" customHeight="1" s="33">
+    <row r="7" ht="188" customHeight="1" s="33">
       <c r="A7" s="4" t="n">
         <v>4</v>
       </c>
@@ -12783,27 +13078,27 @@
       <c r="E7" s="5" t="n"/>
       <c r="F7" s="35" t="inlineStr">
         <is>
-          <t>部分属实</t>
+          <t>属实</t>
         </is>
       </c>
       <c r="G7" s="35" t="inlineStr">
         <is>
-          <t>「cordless impact wrench」2026 年 1–9 月搜索 16.0 万，同比 +5.8%，Q3 同比 +16.5%（卖家精灵 ABA 月度搜索趋势（US，截至 2026-09））；外部需求在增长。</t>
+          <t>领星 ASIN 日报（同期）：H1 $2,314K（月均 $386K），7–9 月 $894K（月均 $298K，−23%）；10 月 1–24 日 $298K，日均 $12.4K，比 9 月日均 $9.6K 回升 30%。「cordless impact wrench」1–9 月搜索同比 +5.8%、Q3 +16.5%（卖家精灵 ABA 月度搜索趋势（US，截至 2026-09））。</t>
         </is>
       </c>
       <c r="H7" s="35" t="inlineStr">
         <is>
-          <t>H2 下滑是内部竞争力问题，不是市场因素。</t>
+          <t>H2 下滑属实，且外部需求在涨，是内部竞争力问题；10 月已明显回暖。</t>
         </is>
       </c>
       <c r="I7" s="35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TOP1 1100N 款毛利低、竞争加剧；高扭矩款推广不足。</t>
         </is>
       </c>
       <c r="J7" s="35" t="inlineStr">
         <is>
-          <t>资源集中到高扭矩、高毛利款，跟上需求增长。</t>
+          <t>Q4 主推 1600N / 2200N 正毛利款，跟上需求增长。</t>
         </is>
       </c>
       <c r="K7" s="35" t="inlineStr">
@@ -12813,7 +13108,7 @@
       </c>
       <c r="L7" s="35" t="inlineStr">
         <is>
-          <t>2027-01-31</t>
+          <t>2026-12-31</t>
         </is>
       </c>
       <c r="M7" s="35" t="inlineStr">
@@ -12823,7 +13118,7 @@
       </c>
       <c r="N7" s="35" t="inlineStr">
         <is>
-          <t>待启动</t>
+          <t>进行中</t>
         </is>
       </c>
       <c r="O7" s="35" t="inlineStr">
@@ -12832,7 +13127,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="90" customHeight="1" s="33">
+    <row r="8" ht="202" customHeight="1" s="33">
       <c r="A8" s="4" t="n">
         <v>5</v>
       </c>
@@ -12854,27 +13149,27 @@
       <c r="E8" s="5" t="n"/>
       <c r="F8" s="35" t="inlineStr">
         <is>
-          <t>部分属实</t>
+          <t>属实</t>
         </is>
       </c>
       <c r="G8" s="35" t="inlineStr">
         <is>
-          <t>V1：12 个负毛利 ASIN 合计收入 $72,687、亏损 $7,701，集中在 900N / 340N 低扭矩段；V2.9 品类整体 GM 5.92%，负毛利面可能更大。</t>
+          <t>利润表（领星利润报表-MSKU，2026-01-01~10-24）：负毛利 ASIN 21 个，合计销售 $131,769（3.9%）、亏 $14,827。最大亏损：B0DHVSTCWP（1100N+电池套装，销售 $1,140、亏 $3,796）、B0DRJLZ2QL（1100N Natbeesy，亏 $3,621、广告 27.0%）、B0DYNXZBS8（900N，广告 34.8%）。</t>
         </is>
       </c>
       <c r="H8" s="35" t="inlineStr">
         <is>
-          <t>按 V2.9 重算负毛利 ASIN。</t>
+          <t>负毛利 ASIN 从 V1 的 12 个修正为 21 个，亏损从 $7,701 修正为 $14,827；失血集中在 900–1100N，340N 段整体 GM 20.3%（V1 的 −17.75% 只代表个别款）。</t>
         </is>
       </c>
       <c r="I8" s="35" t="inlineStr">
         <is>
-          <t>低扭矩价格带被白牌压到盈亏线以下。</t>
+          <t>低扭矩段价格带被压到盈亏线；套装款成本结构不合理。</t>
         </is>
       </c>
       <c r="J8" s="35" t="inlineStr">
         <is>
-          <t>340N / 900N 负毛利款停广告并清货。</t>
+          <t>21 个负毛利 ASIN：套装款停售，单机款停广告并清货。</t>
         </is>
       </c>
       <c r="K8" s="35" t="inlineStr">
@@ -12889,7 +13184,7 @@
       </c>
       <c r="M8" s="35" t="inlineStr">
         <is>
-          <t>$8–15K</t>
+          <t>$12–18K/年</t>
         </is>
       </c>
       <c r="N8" s="35" t="inlineStr">
@@ -12903,7 +13198,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="104" customHeight="1" s="33">
+    <row r="9" ht="146" customHeight="1" s="33">
       <c r="A9" s="4" t="n">
         <v>6</v>
       </c>
@@ -12930,12 +13225,12 @@
       </c>
       <c r="G9" s="35" t="inlineStr">
         <is>
-          <t>6 个 SKU 广告费率 &gt;25%，最高 41.5%（B0G48N2VLW，GM 0.00%）；核心词 PPC 建议竞价 $1.71、均价 $85.49（卖家精灵 2026-09）。</t>
+          <t>利润表（领星利润报表-MSKU，2026-01-01~10-24）：广告费率 &gt;25% 的 ASIN 6 个，覆盖销售 $110,269；品类广告费率 13.68%，低于公司 14.82%。核心词 PPC 建议竞价 $1.71、均价 $85.49（卖家精灵 2026-09）。</t>
         </is>
       </c>
       <c r="H9" s="35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>与 V1 一致（V1 6 个、整体 16.95%）。</t>
         </is>
       </c>
       <c r="I9" s="35" t="inlineStr">
@@ -12945,7 +13240,7 @@
       </c>
       <c r="J9" s="35" t="inlineStr">
         <is>
-          <t>6 个 SKU 设 ACOS 上限 = 保本，未达标停投。</t>
+          <t>6 个 ASIN 设 ACOS 上限 = 保本，未达标停投。</t>
         </is>
       </c>
       <c r="K9" s="35" t="inlineStr">
@@ -12999,8 +13294,6 @@
       <c r="D12" s="9" t="n"/>
       <c r="E12" s="9" t="n"/>
     </row>
-    <row r="13"/>
-    <row r="14"/>
     <row r="15" ht="24" customHeight="1" s="33">
       <c r="A15" s="2" t="inlineStr">
         <is>
@@ -13015,7 +13308,6 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
     <row r="18" ht="24" customHeight="1" s="33">
       <c r="A18" s="11" t="inlineStr">
         <is>
@@ -13155,7 +13447,7 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="64" customHeight="1" s="33">
+    <row r="21" ht="90" customHeight="1" s="33">
       <c r="A21" s="4" t="n">
         <v>2</v>
       </c>
@@ -13186,17 +13478,17 @@
       </c>
       <c r="G21" s="35" t="inlineStr">
         <is>
-          <t>2200N+ 线 GM 22.84%（V1），需 V2.9 口径复核</t>
+          <t>利润表（领星利润报表-MSKU，2026-01-01~10-24）：2200N 段 GM 23.4%、ASP $140.3、广告 10.5%；1600N GM 16.0%</t>
         </is>
       </c>
       <c r="H21" s="35" t="inlineStr">
         <is>
-          <t>新品与预算向 1500N+ / 2200N+ 倾斜</t>
+          <t>新品与预算向 1600N / 2200N 倾斜</t>
         </is>
       </c>
       <c r="I21" s="35" t="inlineStr">
         <is>
-          <t>$200–400K</t>
+          <t>$300–500K</t>
         </is>
       </c>
       <c r="J21" s="35" t="inlineStr">
@@ -13505,8 +13797,6 @@
       <c r="D28" s="9" t="n"/>
       <c r="E28" s="9" t="n"/>
     </row>
-    <row r="29"/>
-    <row r="30"/>
     <row r="31" ht="24" customHeight="1" s="33">
       <c r="A31" s="13" t="inlineStr">
         <is>
@@ -13677,12 +13967,12 @@
       </c>
       <c r="G34" s="35" t="inlineStr">
         <is>
-          <t>340N / 900N 价格带竞品价格</t>
+          <t>利润表（领星利润报表-MSKU，2026-01-01~10-24）：900N GM 5.2%、1000N GM −0.7%、1100N GM 9.6%；340N 整体 GM 20.3%</t>
         </is>
       </c>
       <c r="H34" s="35" t="inlineStr">
         <is>
-          <t>退出低扭矩负毛利段</t>
+          <t>退出 900–1000N 负毛利段，1100N 提价/降本</t>
         </is>
       </c>
       <c r="I34" s="35" t="inlineStr">
@@ -13707,7 +13997,7 @@
       </c>
       <c r="M34" s="35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>340N 不是整体亏损，需逐款看</t>
         </is>
       </c>
     </row>
@@ -13742,17 +14032,17 @@
       </c>
       <c r="G35" s="35" t="inlineStr">
         <is>
-          <t>V2.9 口径下美国站毛利</t>
+          <t>利润表（领星利润报表-MSKU，2026-01-01~10-24）：美国 GM 13.3%、广告 15.0%，德国 GM 22.1%</t>
         </is>
       </c>
       <c r="H35" s="35" t="inlineStr">
         <is>
-          <t>口径确认后调整预算</t>
+          <t>预算向德国、法国倾斜</t>
         </is>
       </c>
       <c r="I35" s="35" t="inlineStr">
         <is>
-          <t>数据</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J35" s="35" t="inlineStr">
@@ -14191,8 +14481,6 @@
       <c r="D44" s="9" t="n"/>
       <c r="E44" s="9" t="n"/>
     </row>
-    <row r="45"/>
-    <row r="46"/>
     <row r="47" ht="24" customHeight="1" s="33">
       <c r="A47" s="15" t="inlineStr">
         <is>
@@ -14210,8 +14498,8 @@
     <row r="49" ht="56" customHeight="1" s="33">
       <c r="A49" s="38" t="inlineStr">
         <is>
-          <t>1）口径：V2.9 基线 $438,040 / 21 ASIN / GM 5.92%，与 V1 约 $2.40M / 85 ASIN / GM 13.48% 差距巨大，必须先确认品类范围；
-2）高扭矩段的真实毛利与可放量空间；
+          <t>1）口径：利润表 $3.42M / 103 ASIN / GM 14.48%，与 V1（约 $2.40M、85 ASIN、GM 13.48%）基本一致，V2.9 基线（$438K / 21 ASIN）范围不完整，后续以利润表为准；
+2）TOP1 B0CTKFKGL9（1100N，占 12.9%）毛利率只有 5.2%，需要采购给出降本空间；
 3）在售款合规（UL 2595 / UL 62133 / UN38.3）覆盖率。</t>
         </is>
       </c>
@@ -14230,7 +14518,6 @@
       <c r="N49" s="39" t="n"/>
       <c r="O49" s="40" t="n"/>
     </row>
-    <row r="50"/>
     <row r="51" ht="22" customHeight="1" s="33">
       <c r="A51" s="16" t="inlineStr">
         <is>
@@ -14241,8 +14528,8 @@
     <row r="52" ht="40" customHeight="1" s="33">
       <c r="A52" s="38" t="inlineStr">
         <is>
-          <t>需修改：V1 的 27 年目标 $5.28M（×2.2）在 V2.9 口径下（2–9 月 $438K，年化约 $0.66M）无法实现。
-建议：先确认口径。若以 V2.9 为准，目标设 $0.8–1.0M、毛利率 ≥12%；若 V1 口径成立，增长倍数从 ×2.2 降到 ×1.25–1.45（约 $3.0–3.5M），毛利率 ≥15%。</t>
+          <t>建议：27 年目标从 $5.28M 调到 $4.6–4.8M，毛利率目标 ≥16%（当前 14.48%）。
+理由：利润表 1–10/24 为 $3.42M，年化约 $4.2M，$5.28M 需增长 26%；市场需求只 +5.8%，H2 月均比 H1 低 23%，增长要靠 1600N / 2200N 和德国/法国，不宜按 ×2.2 设定。</t>
         </is>
       </c>
       <c r="B52" s="39" t="n"/>
@@ -14260,7 +14547,6 @@
       <c r="N52" s="39" t="n"/>
       <c r="O52" s="40" t="n"/>
     </row>
-    <row r="53"/>
     <row r="54" ht="22" customHeight="1" s="33">
       <c r="A54" s="16" t="inlineStr">
         <is>
@@ -14271,8 +14557,8 @@
     <row r="55" ht="40" customHeight="1" s="33">
       <c r="A55" s="38" t="inlineStr">
         <is>
-          <t>最大威胁：低扭矩段结构性亏损+品类毛利率偏低（V2.9 为 5.92%），在需求增长（Q3 搜索 +16.5%）的市场里反而失速。
-应对：①退出低扭矩负毛利段；②资源集中到 1500N+ / 2200N+；③合规全量排查；④长尾站点清理。</t>
+          <t>最大威胁：低扭矩段（900–1100N，占 38.1%、GM &lt;10%）被白牌持续压价，而 TOP1 就在这一段（GM 5.2%）。
+应对：①1100N 提价/降本，900–1000N 清理；②资源集中到 1600N / 2200N；③合规全量排查；④长尾 ASIN 清理。</t>
         </is>
       </c>
       <c r="B55" s="39" t="n"/>
@@ -14290,7 +14576,6 @@
       <c r="N55" s="39" t="n"/>
       <c r="O55" s="40" t="n"/>
     </row>
-    <row r="56"/>
     <row r="57" ht="22" customHeight="1" s="33">
       <c r="A57" s="16" t="inlineStr">
         <is>
@@ -14323,7 +14608,6 @@
       <c r="N58" s="39" t="n"/>
       <c r="O58" s="40" t="n"/>
     </row>
-    <row r="59"/>
     <row r="60" ht="22" customHeight="1" s="33">
       <c r="A60" s="16" t="inlineStr">
         <is>
@@ -14517,7 +14801,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="174" customHeight="1" s="33">
+    <row r="4" ht="188" customHeight="1" s="33">
       <c r="A4" s="4" t="n">
         <v>1</v>
       </c>
@@ -14544,12 +14828,12 @@
       </c>
       <c r="G4" s="35" t="inlineStr">
         <is>
-          <t>工作台 V2.9 基线：灯具 $1,713,290、占公司 6.59%、毛利率 17.63%（七个品类中最高）、广告费率 14.55%、82 个 ASIN。</t>
+          <t>利润表（领星利润报表-MSKU，2026-01-01~10-24）：灯具销售额 $3,088,508（占公司 9.45%），毛利 $586,484（占 13.04%），毛利率 18.99%（七品类第二），广告费率 14.65%，132 个 ASIN。分类：工作灯 56.3%（GM 16.6%）、锂电池工作灯 29.6%（GM 24.5%）、车库灯 4.0%、支架灯 3.3%。</t>
         </is>
       </c>
       <c r="H4" s="35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>收入仍 100% 来自工作灯类产品；锂电池工作灯毛利率 24.5%，是现有最好的方向。</t>
         </is>
       </c>
       <c r="I4" s="35" t="inlineStr">
@@ -14588,7 +14872,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="76" customHeight="1" s="33">
+    <row r="5" ht="160" customHeight="1" s="33">
       <c r="A5" s="4" t="n">
         <v>2</v>
       </c>
@@ -14615,12 +14899,12 @@
       </c>
       <c r="G5" s="35" t="inlineStr">
         <is>
-          <t>美国 GM 15.39% 占 82.5%；加拿大 GM 28.59% 仅占 11.9%；墨西哥 52 个 ASIN 只产出 $3,998。</t>
+          <t>利润表（领星利润报表-MSKU，2026-01-01~10-24）：美国 80.9%（GM 17.7%、广告 16.0%）；加拿大 13.2%（GM 23.1%、广告 9.7%）；德国 2.3%（GM 27.7%）；法国 1.9%（GM 25.4%、广告 5.1%）；英国 0.5%（GM 29.1%）。</t>
         </is>
       </c>
       <c r="H5" s="35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>美国毛利率修正为 17.7%（V1 15.39%），加拿大 23.1%（V1 28.59%）；欧洲毛利率 25–29%，结构优化方向不变。</t>
         </is>
       </c>
       <c r="I5" s="35" t="inlineStr">
@@ -14630,12 +14914,12 @@
       </c>
       <c r="J5" s="35" t="inlineStr">
         <is>
-          <t>加拿大补库存、加预算；墨西哥只保留产出 Top 款。</t>
+          <t>加拿大补库存、加预算；德国、法国扩款；墨西哥只保留产出 Top 款。</t>
         </is>
       </c>
       <c r="K5" s="35" t="inlineStr">
         <is>
-          <t>北美运营</t>
+          <t>北美运营 / 欧洲运营</t>
         </is>
       </c>
       <c r="L5" s="35" t="inlineStr">
@@ -14645,7 +14929,7 @@
       </c>
       <c r="M5" s="35" t="inlineStr">
         <is>
-          <t>$50–100K 毛利（V1 ≈$33 万为 8 个月口径的理论上限）</t>
+          <t>$40–60K 毛利</t>
         </is>
       </c>
       <c r="N5" s="35" t="inlineStr">
@@ -14686,7 +14970,7 @@
       </c>
       <c r="G6" s="35" t="inlineStr">
         <is>
-          <t>灯具毛利率 17.63% 为七品类最高；ASP $30.17 低于公司 $47.13。</t>
+          <t>利润表（领星利润报表-MSKU，2026-01-01~10-24）：工作灯 ASP $27.7、锂电池工作灯 $33.2、支架灯 $65.6、AC 4 个装支架灯 $130.4；高价支架款毛利率 18–22%，与主力持平。</t>
         </is>
       </c>
       <c r="H6" s="35" t="inlineStr">
@@ -14730,7 +15014,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="104" customHeight="1" s="33">
+    <row r="7" ht="230" customHeight="1" s="33">
       <c r="A7" s="4" t="n">
         <v>4</v>
       </c>
@@ -14757,12 +15041,12 @@
       </c>
       <c r="G7" s="35" t="inlineStr">
         <is>
-          <t>16 个 ASIN 毛利为负，合计亏损 $21,068；10 个 ASIN 广告占比 &gt;25%（涉及销售额 $142,176）；9 个 ASIN 9 月零销量。</t>
+          <t>利润表（领星利润报表-MSKU，2026-01-01~10-24）：29 个 ASIN 毛利为负，合计销售 $169,053、亏 $24,926；11 个 ASIN 广告费率 &gt;25%（覆盖销售 $147,538）；12 个零销售。最大亏损：四叶草款 B0H2L5WSJ7（亏 $6,573、广告 44.0%）、B0H2L522Q5（亏 $5,867、广告 46.0%）、方形 16 珠 21W B0BD8LB4T1（亏 $4,362、广告 34.2%）。</t>
         </is>
       </c>
       <c r="H7" s="35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>负毛利从 V1 的 16 个/$21,068 修正为 29 个/$24,926；亏损集中在四叶草新款和方形 16 珠老款。</t>
         </is>
       </c>
       <c r="I7" s="35" t="inlineStr">
@@ -14872,7 +15156,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="90" customHeight="1" s="33">
+    <row r="9" ht="132" customHeight="1" s="33">
       <c r="A9" s="4" t="n">
         <v>6</v>
       </c>
@@ -14899,12 +15183,12 @@
       </c>
       <c r="G9" s="35" t="inlineStr">
         <is>
-          <t>V2.9：灯具占公司 6.59%，与 V1 目标占比一致；毛利率 17.63% 为七品类最高。</t>
+          <t>利润表（领星利润报表-MSKU，2026-01-01~10-24）：灯具占公司销售 9.45%、毛利 13.04%，毛利率 18.99%；带「26新品」标签的 28 个 ASIN 占 30.7%、GM 23.4%（老品 17.0%）——新品孵化是七品类中最成功的。</t>
         </is>
       </c>
       <c r="H9" s="35" t="inlineStr">
         <is>
-          <t>高毛利品类应给更高增长倍数，但需以新品线立项为前提。</t>
+          <t>新品成功、毛利高、10 月增长强，应给予差异化增长倍数。</t>
         </is>
       </c>
       <c r="I9" s="35" t="inlineStr">
@@ -14950,14 +15234,80 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="21" customHeight="1" s="33">
+    <row r="11" ht="104" customHeight="1" s="33">
       <c r="A11" s="8" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="9" t="n"/>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="9" t="n"/>
-      <c r="E11" s="9" t="n"/>
+      <c r="B11" s="36" t="inlineStr">
+        <is>
+          <t>Q4 旺季已启动，需要备货跟上</t>
+        </is>
+      </c>
+      <c r="C11" s="36" t="inlineStr">
+        <is>
+          <t>领星 ASIN 日报（同期）：4 月 $242K 为低点 → 9 月 $364K → 10 月 1–24 日 $478K，日均 $19.9K，比 9 月日均 $12.1K 增长 64%</t>
+        </is>
+      </c>
+      <c r="D11" s="36" t="inlineStr">
+        <is>
+          <t>若 11–12 月断货，错失全年最大窗口</t>
+        </is>
+      </c>
+      <c r="E11" s="36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="41" t="inlineStr">
+        <is>
+          <t>属实</t>
+        </is>
+      </c>
+      <c r="G11" s="41" t="inlineStr">
+        <is>
+          <t>来源：领星 ASIN 日报（同期）；ABA「work light」11 月为全年搜索峰值</t>
+        </is>
+      </c>
+      <c r="H11" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I11" s="41" t="inlineStr">
+        <is>
+          <t>冬季照明+节日礼品需求</t>
+        </is>
+      </c>
+      <c r="J11" s="41" t="inlineStr">
+        <is>
+          <t>按 10 月日均 ×1.2 重算 11–12 月备货；锂电池三头款等正毛利主力优先</t>
+        </is>
+      </c>
+      <c r="K11" s="41" t="inlineStr">
+        <is>
+          <t>计划 / 运营</t>
+        </is>
+      </c>
+      <c r="L11" s="41" t="inlineStr">
+        <is>
+          <t>2026-11-05</t>
+        </is>
+      </c>
+      <c r="M11" s="41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N11" s="41" t="inlineStr">
+        <is>
+          <t>进行中</t>
+        </is>
+      </c>
+      <c r="O11" s="41" t="inlineStr">
+        <is>
+          <t>新增项</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="21" customHeight="1" s="33">
       <c r="A12" s="8" t="n">
@@ -14968,7 +15318,6 @@
       <c r="D12" s="9" t="n"/>
       <c r="E12" s="9" t="n"/>
     </row>
-    <row r="13"/>
     <row r="14" ht="24" customHeight="1" s="33">
       <c r="A14" s="2" t="inlineStr">
         <is>
@@ -14983,7 +15332,6 @@
         </is>
       </c>
     </row>
-    <row r="16"/>
     <row r="17" ht="24" customHeight="1" s="33">
       <c r="A17" s="11" t="inlineStr">
         <is>
@@ -15343,8 +15691,6 @@
       <c r="D25" s="9" t="n"/>
       <c r="E25" s="9" t="n"/>
     </row>
-    <row r="26"/>
-    <row r="27"/>
     <row r="28" ht="24" customHeight="1" s="33">
       <c r="A28" s="13" t="inlineStr">
         <is>
@@ -15834,8 +16180,6 @@
       <c r="D38" s="9" t="n"/>
       <c r="E38" s="9" t="n"/>
     </row>
-    <row r="39"/>
-    <row r="40"/>
     <row r="41" ht="24" customHeight="1" s="33">
       <c r="A41" s="15" t="inlineStr">
         <is>
@@ -15853,9 +16197,9 @@
     <row r="43" ht="56" customHeight="1" s="33">
       <c r="A43" s="38" t="inlineStr">
         <is>
-          <t>1）应急灯、露营灯新品线能否在 2027 年飓风季（6 月）前上市；
-2）口径：V1 写「27 年目标 $3.77M = 统一 1.1 倍增长」，反推基数约 $3.4M，而 V2.9 2–9 月为 $1.71M（年化约 $2.57M），需统一；
-3）锂电合规（UN38.3 / UL）覆盖率。</t>
+          <t>1）Q4 旺季：10 月日均比 9 月增长 64%，11–12 月备货是否够；
+2）新品方向：26 新品 28 个 ASIN 占 30.7%、GM 23.4%，锂电池工作灯 GM 24.5%，但四叶草款广告 44–46% 在亏，需要逐款复盘；
+3）应急灯、露营灯新品线能否在 2027 年飓风季（6 月）前上市。</t>
         </is>
       </c>
       <c r="B43" s="39" t="n"/>
@@ -15873,7 +16217,6 @@
       <c r="N43" s="39" t="n"/>
       <c r="O43" s="40" t="n"/>
     </row>
-    <row r="44"/>
     <row r="45" ht="22" customHeight="1" s="33">
       <c r="A45" s="16" t="inlineStr">
         <is>
@@ -15884,8 +16227,8 @@
     <row r="46" ht="40" customHeight="1" s="33">
       <c r="A46" s="38" t="inlineStr">
         <is>
-          <t>建议：维持 $3.77M 目标，暂不上调到 $4.6–5.0M；毛利率目标 ≥17%（V2.9 为 17.63%）。
-理由：上调依赖应急/露营新品线，在立项与上市时间确认前不宜写进目标；新品立项通过后再上调 $0.5–0.8M。</t>
+          <t>建议上调：27 年目标从 $3.77M 调到 $4.2–4.5M，毛利率目标 ≥19%。
+理由：利润表 1–10/24 为 $3.09M（年化约 $3.8M），$3.77M 只是持平；灯具毛利率 18.99%、新品毛利 23.4%、10 月增长 64%，是最值得加码的品类。若应急/露营新品线立项通过，可再上调到 V1 建议的 $4.6–5.0M。</t>
         </is>
       </c>
       <c r="B46" s="39" t="n"/>
@@ -15903,7 +16246,6 @@
       <c r="N46" s="39" t="n"/>
       <c r="O46" s="40" t="n"/>
     </row>
-    <row r="47"/>
     <row r="48" ht="22" customHeight="1" s="33">
       <c r="A48" s="16" t="inlineStr">
         <is>
@@ -15933,7 +16275,6 @@
       <c r="N49" s="39" t="n"/>
       <c r="O49" s="40" t="n"/>
     </row>
-    <row r="50"/>
     <row r="51" ht="22" customHeight="1" s="33">
       <c r="A51" s="16" t="inlineStr">
         <is>
@@ -15965,7 +16306,6 @@
       <c r="N52" s="39" t="n"/>
       <c r="O52" s="40" t="n"/>
     </row>
-    <row r="53"/>
     <row r="54" ht="22" customHeight="1" s="33">
       <c r="A54" s="16" t="inlineStr">
         <is>
